--- a/samples/sample_rep_opd_2569-09.xlsx
+++ b/samples/sample_rep_opd_2569-09.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="REP" sheetId="1" r:id="rId1"/>
+    <sheet name="รายละเอียด(ข้อมูลปกติ) 1 OP" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -399,685 +399,189 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T59"/>
+  <dimension ref="A1:AD65"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>รายงานผลการพิจารณาจ่ายชดเชย (ข้อมูลตัวอย่าง)</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>หน่วยบริการ: 99999 โรงพยาบาลทดสอบ</v>
+        <v>ออกรายงานวันที่ 05/10/2569 เวลา 09:39 (ข้อมูลตัวอย่าง)</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>โรงพยาบาล 99999 รพ.ทดสอบ</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>REP No.</v>
-      </c>
-      <c r="B4" t="str">
-        <v>TRAN_ID</v>
-      </c>
-      <c r="C4" t="str">
-        <v>HN</v>
-      </c>
-      <c r="D4" t="str">
-        <v>AN</v>
-      </c>
-      <c r="E4" t="str">
-        <v>PID</v>
-      </c>
-      <c r="F4" t="str">
-        <v>ชื่อ-สกุล</v>
-      </c>
-      <c r="G4" t="str">
-        <v>วันเข้ารักษา</v>
-      </c>
-      <c r="H4" t="str">
-        <v>สิทธิ</v>
-      </c>
-      <c r="I4" t="str">
-        <v>เรียกเก็บ</v>
-      </c>
-      <c r="J4" t="str">
-        <v>ชดเชยสุทธิ</v>
-      </c>
-      <c r="K4" t="str">
-        <v>ERROR CODE</v>
-      </c>
-      <c r="L4" t="str">
-        <v>HC</v>
-      </c>
-      <c r="N4" t="str">
-        <v>AE</v>
-      </c>
-      <c r="P4" t="str">
-        <v>INST</v>
-      </c>
-      <c r="Q4" t="str">
-        <v>DMIS</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="L5" t="str">
-        <v>HC</v>
-      </c>
-      <c r="M5" t="str">
-        <v>DRUG</v>
-      </c>
-      <c r="N5" t="str">
-        <v>AE</v>
-      </c>
-      <c r="O5" t="str">
-        <v>DRUG</v>
-      </c>
-      <c r="Q5" t="str">
-        <v>ยอดชดเชยที่จ่ายจริง</v>
-      </c>
-      <c r="R5" t="str">
-        <v>DMISHD</v>
-      </c>
-      <c r="S5" t="str">
-        <v>Palliative care</v>
-      </c>
-      <c r="T5" t="str">
-        <v>PP</v>
+        <v>จังหวัด ทดสอบ</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B6" t="str">
-        <v>T260903000002</v>
-      </c>
-      <c r="C6" t="str">
-        <v>000000015</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6" t="str">
-        <v>3100000118785</v>
-      </c>
-      <c r="F6" t="str">
-        <v>นายทดสอบ15 สมมติ</v>
-      </c>
-      <c r="G6" s="1">
-        <v>46268</v>
-      </c>
-      <c r="H6" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I6">
-        <v>274</v>
-      </c>
-      <c r="J6">
-        <v>274</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6">
-        <v>0</v>
-      </c>
-      <c r="P6">
-        <v>0</v>
-      </c>
-      <c r="Q6">
-        <v>0</v>
-      </c>
-      <c r="R6">
-        <v>0</v>
-      </c>
-      <c r="S6">
-        <v>0</v>
-      </c>
-      <c r="T6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B7" t="str">
-        <v>T260903000032</v>
-      </c>
-      <c r="C7" t="str">
-        <v>000000025</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7" t="str">
-        <v>3100000197975</v>
-      </c>
-      <c r="F7" t="str">
-        <v>นายทดสอบ25 สมมติ</v>
-      </c>
-      <c r="G7" t="str">
-        <v>03/09/2569</v>
-      </c>
-      <c r="H7" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I7">
-        <v>584</v>
-      </c>
-      <c r="J7">
-        <v>584</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7">
-        <v>0</v>
-      </c>
-      <c r="P7">
-        <v>0</v>
-      </c>
-      <c r="Q7">
-        <v>0</v>
-      </c>
-      <c r="R7">
-        <v>0</v>
-      </c>
-      <c r="S7">
-        <v>0</v>
-      </c>
-      <c r="T7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B8" t="str">
-        <v>T260903000062</v>
-      </c>
-      <c r="C8" t="str">
-        <v>000000035</v>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v>3100000277165</v>
-      </c>
-      <c r="F8" t="str">
-        <v>นายทดสอบ35 สมมติ</v>
-      </c>
-      <c r="G8" s="1">
-        <v>46268</v>
-      </c>
-      <c r="H8" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I8">
-        <v>894</v>
-      </c>
-      <c r="J8">
-        <v>894</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8">
-        <v>0</v>
-      </c>
-      <c r="P8">
-        <v>0</v>
-      </c>
-      <c r="Q8">
-        <v>0</v>
-      </c>
-      <c r="R8">
-        <v>0</v>
-      </c>
-      <c r="S8">
-        <v>0</v>
-      </c>
-      <c r="T8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B9" t="str">
-        <v>T260904000033</v>
-      </c>
-      <c r="C9" t="str">
-        <v>000000032</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9" t="str">
-        <v>3100000253408</v>
-      </c>
-      <c r="F9" t="str">
-        <v>นางทดสอบ32 สมมติ</v>
-      </c>
-      <c r="G9" s="1">
-        <v>46269</v>
-      </c>
-      <c r="H9" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I9">
-        <v>621</v>
-      </c>
-      <c r="J9">
-        <v>621</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>2240</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
-        <v>0</v>
-      </c>
-      <c r="T9">
-        <v>0</v>
+        <v>เลขที่เอกสาร 99999 OPUCS256909 01</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B10" t="str">
-        <v>T260904000063</v>
-      </c>
-      <c r="C10" t="str">
-        <v>000000002</v>
-      </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10" t="str">
-        <v>3100000015838</v>
-      </c>
-      <c r="F10" t="str">
-        <v>นางทดสอบ2 สมมติ</v>
-      </c>
-      <c r="G10" t="str">
-        <v>04/09/2569</v>
-      </c>
-      <c r="H10" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I10">
-        <v>1051</v>
-      </c>
-      <c r="J10">
-        <v>1051</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10">
-        <v>0</v>
-      </c>
-      <c r="P10">
-        <v>0</v>
-      </c>
-      <c r="Q10">
-        <v>0</v>
-      </c>
-      <c r="R10">
-        <v>0</v>
-      </c>
-      <c r="S10">
-        <v>0</v>
-      </c>
-      <c r="T10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B11" t="str">
-        <v>T260905000004</v>
-      </c>
-      <c r="C11" t="str">
-        <v>000000029</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v>3100000229651</v>
-      </c>
-      <c r="F11" t="str">
-        <v>นายทดสอบ29 สมมติ</v>
-      </c>
-      <c r="G11" s="1">
-        <v>46270</v>
-      </c>
-      <c r="H11" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I11">
-        <v>348</v>
-      </c>
-      <c r="J11">
-        <v>348</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>0</v>
-      </c>
-      <c r="Q11">
-        <v>0</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
+        <v>ข้อมูลปกติ</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>6909002</v>
+        <v>REP</v>
       </c>
       <c r="B12" t="str">
-        <v>T260905000034</v>
+        <v>ลำดับที่</v>
       </c>
       <c r="C12" t="str">
-        <v>000000039</v>
+        <v>TRAN_ID</v>
       </c>
       <c r="D12" t="str">
-        <v/>
+        <v>HN</v>
       </c>
       <c r="E12" t="str">
-        <v>3100000308841</v>
+        <v>AN</v>
       </c>
       <c r="F12" t="str">
-        <v>นายทดสอบ39 สมมติ</v>
+        <v>PID</v>
       </c>
       <c r="G12" t="str">
-        <v>05/09/2569</v>
+        <v>ชื่อ - สกุล</v>
       </c>
       <c r="H12" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I12">
-        <v>658</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
+        <v>วันเข้ารักษา</v>
+      </c>
+      <c r="I12" t="str">
+        <v>วันจำหน่าย</v>
+      </c>
+      <c r="J12" t="str">
+        <v>MAININSCL</v>
       </c>
       <c r="K12" t="str">
-        <v>C438</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
-      <c r="P12">
-        <v>0</v>
-      </c>
-      <c r="Q12">
-        <v>0</v>
-      </c>
-      <c r="R12">
-        <v>0</v>
-      </c>
-      <c r="S12">
-        <v>0</v>
-      </c>
-      <c r="T12">
-        <v>0</v>
+        <v>PROJCODE</v>
+      </c>
+      <c r="L12" t="str">
+        <v>เรียกเก็บ</v>
+      </c>
+      <c r="M12" t="str">
+        <v>กองทุน IP</v>
+      </c>
+      <c r="O12" t="str">
+        <v>ยอดจ่ายชดเชย</v>
+      </c>
+      <c r="AD12" t="str">
+        <v>ยอดชดเชยทั้งสิ้น</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B13" t="str">
-        <v>T260905000064</v>
-      </c>
-      <c r="C13" t="str">
-        <v>000000009</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v>3100000071271</v>
-      </c>
-      <c r="F13" t="str">
-        <v>นายทดสอบ9 สมมติ</v>
-      </c>
-      <c r="G13" s="1">
-        <v>46270</v>
-      </c>
-      <c r="H13" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I13">
-        <v>968</v>
-      </c>
-      <c r="J13">
-        <v>968</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>3360</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
-        <v>0</v>
-      </c>
-      <c r="Q13">
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
+      <c r="M13" t="str">
+        <v>พรบ.</v>
+      </c>
+      <c r="N13" t="str">
+        <v>AdjRW</v>
+      </c>
+      <c r="O13" t="str">
+        <v>OP</v>
+      </c>
+      <c r="P13" t="str">
+        <v>IP</v>
+      </c>
+      <c r="R13" t="str">
+        <v>HC</v>
+      </c>
+      <c r="T13" t="str">
+        <v>AE</v>
+      </c>
+      <c r="V13" t="str">
+        <v>INST</v>
+      </c>
+      <c r="W13" t="str">
+        <v>DMIS</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>Palliative care</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>DMISHD</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>PP</v>
+      </c>
+      <c r="AC13" t="str">
+        <v>FS</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B14" t="str">
-        <v>T260908000007</v>
-      </c>
-      <c r="C14" t="str">
-        <v>000000010</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v>3100000079190</v>
-      </c>
-      <c r="F14" t="str">
-        <v>นางทดสอบ10 สมมติ</v>
-      </c>
-      <c r="G14" t="str">
-        <v>08/09/2569</v>
-      </c>
-      <c r="H14" t="str">
-        <v>UCS</v>
-      </c>
-      <c r="I14">
-        <v>459</v>
-      </c>
-      <c r="J14">
-        <v>459</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
+      <c r="M14" t="str">
+        <v>(2)</v>
+      </c>
+      <c r="N14" t="str">
+        <v>(3)</v>
+      </c>
+      <c r="P14" t="str">
+        <v>ยอดชดเชยที่คำนวณได้</v>
+      </c>
+      <c r="Q14" t="str">
+        <v>ยอดชดเชยที่จ่ายจริง</v>
+      </c>
+      <c r="R14" t="str">
+        <v>HC</v>
+      </c>
+      <c r="S14" t="str">
+        <v>DRUG</v>
+      </c>
+      <c r="T14" t="str">
+        <v>AE</v>
+      </c>
+      <c r="U14" t="str">
+        <v>DRUG</v>
+      </c>
+      <c r="W14" t="str">
+        <v>ยอดชดเชยที่คำนวณได้</v>
+      </c>
+      <c r="X14" t="str">
+        <v>ยอดชดเชยที่จ่ายจริง</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>DMIS_DRUG</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B15" t="str">
-        <v>T260908000037</v>
+        <v>6909001</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
       </c>
       <c r="C15" t="str">
-        <v>000000020</v>
+        <v>T260903000002</v>
       </c>
       <c r="D15" t="str">
-        <v/>
+        <v>000000015</v>
       </c>
       <c r="E15" t="str">
-        <v>3100000158380</v>
+        <v/>
       </c>
       <c r="F15" t="str">
-        <v>นางทดสอบ20 สมมติ</v>
-      </c>
-      <c r="G15" s="1">
-        <v>46273</v>
-      </c>
-      <c r="H15" t="str">
+        <v>3100000118785</v>
+      </c>
+      <c r="G15" t="str">
+        <v>นายทดสอบ15 สมมติ</v>
+      </c>
+      <c r="H15" s="1">
+        <v>46268</v>
+      </c>
+      <c r="I15" s="1">
+        <v>46268</v>
+      </c>
+      <c r="J15" t="str">
         <v>UCS</v>
       </c>
-      <c r="I15">
-        <v>769</v>
-      </c>
-      <c r="J15">
-        <v>769</v>
-      </c>
       <c r="K15" t="str">
         <v/>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="M15">
         <v>0</v>
@@ -1086,7 +590,7 @@
         <v>0</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>274</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -1102,44 +606,74 @@
       </c>
       <c r="T15">
         <v>0</v>
+      </c>
+      <c r="U15">
+        <v>0</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0</v>
+      </c>
+      <c r="X15">
+        <v>0</v>
+      </c>
+      <c r="Y15">
+        <v>0</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+      <c r="AA15">
+        <v>0</v>
+      </c>
+      <c r="AB15">
+        <v>0</v>
+      </c>
+      <c r="AC15">
+        <v>0</v>
+      </c>
+      <c r="AD15">
+        <v>274</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B16" t="str">
-        <v>T260908000067</v>
+        <v>6909002</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
       </c>
       <c r="C16" t="str">
-        <v>000000030</v>
+        <v>T260903000032</v>
       </c>
       <c r="D16" t="str">
-        <v/>
+        <v>000000025</v>
       </c>
       <c r="E16" t="str">
-        <v>3100000237570</v>
+        <v/>
       </c>
       <c r="F16" t="str">
-        <v>นางทดสอบ30 สมมติ</v>
+        <v>3100000197975</v>
       </c>
       <c r="G16" t="str">
-        <v>08/09/2569</v>
+        <v>นายทดสอบ25 สมมติ</v>
       </c>
       <c r="H16" t="str">
+        <v>03/09/2569</v>
+      </c>
+      <c r="I16" t="str">
+        <v>03/09/2569</v>
+      </c>
+      <c r="J16" t="str">
         <v>UCS</v>
       </c>
-      <c r="I16">
-        <v>279</v>
-      </c>
-      <c r="J16">
-        <v>279</v>
-      </c>
       <c r="K16" t="str">
         <v/>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="M16">
         <v>0</v>
@@ -1148,7 +682,7 @@
         <v>0</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>584</v>
       </c>
       <c r="P16">
         <v>0</v>
@@ -1164,53 +698,83 @@
       </c>
       <c r="T16">
         <v>0</v>
+      </c>
+      <c r="U16">
+        <v>0</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0</v>
+      </c>
+      <c r="X16">
+        <v>0</v>
+      </c>
+      <c r="Y16">
+        <v>0</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+      <c r="AA16">
+        <v>0</v>
+      </c>
+      <c r="AB16">
+        <v>0</v>
+      </c>
+      <c r="AC16">
+        <v>0</v>
+      </c>
+      <c r="AD16">
+        <v>584</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B17" t="str">
-        <v>T260909000008</v>
+        <v>6909003</v>
+      </c>
+      <c r="B17">
+        <v>3</v>
       </c>
       <c r="C17" t="str">
-        <v>000000017</v>
+        <v>T260903000062</v>
       </c>
       <c r="D17" t="str">
-        <v/>
+        <v>000000035</v>
       </c>
       <c r="E17" t="str">
-        <v>3100000134623</v>
+        <v/>
       </c>
       <c r="F17" t="str">
-        <v>นายทดสอบ17 สมมติ</v>
-      </c>
-      <c r="G17" s="1">
-        <v>46274</v>
-      </c>
-      <c r="H17" t="str">
+        <v>3100000277165</v>
+      </c>
+      <c r="G17" t="str">
+        <v>นายทดสอบ35 สมมติ</v>
+      </c>
+      <c r="H17" s="1">
+        <v>46268</v>
+      </c>
+      <c r="I17" s="1">
+        <v>46268</v>
+      </c>
+      <c r="J17" t="str">
         <v>UCS</v>
       </c>
-      <c r="I17">
-        <v>496</v>
-      </c>
-      <c r="J17">
-        <v>496</v>
-      </c>
       <c r="K17" t="str">
         <v/>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="M17">
-        <v>3360</v>
+        <v>0</v>
       </c>
       <c r="N17">
         <v>0</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>894</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -1226,44 +790,74 @@
       </c>
       <c r="T17">
         <v>0</v>
+      </c>
+      <c r="U17">
+        <v>0</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0</v>
+      </c>
+      <c r="X17">
+        <v>0</v>
+      </c>
+      <c r="Y17">
+        <v>0</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+      <c r="AA17">
+        <v>0</v>
+      </c>
+      <c r="AB17">
+        <v>0</v>
+      </c>
+      <c r="AC17">
+        <v>0</v>
+      </c>
+      <c r="AD17">
+        <v>894</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B18" t="str">
-        <v>T260909000068</v>
+        <v>6909002</v>
+      </c>
+      <c r="B18">
+        <v>4</v>
       </c>
       <c r="C18" t="str">
-        <v>000000037</v>
+        <v>T260904000033</v>
       </c>
       <c r="D18" t="str">
-        <v/>
+        <v>000000032</v>
       </c>
       <c r="E18" t="str">
-        <v>3100000293003</v>
+        <v/>
       </c>
       <c r="F18" t="str">
-        <v>นายทดสอบ37 สมมติ</v>
-      </c>
-      <c r="G18" s="1">
-        <v>46274</v>
-      </c>
-      <c r="H18" t="str">
+        <v>3100000253408</v>
+      </c>
+      <c r="G18" t="str">
+        <v>นางทดสอบ32 สมมติ</v>
+      </c>
+      <c r="H18" s="1">
+        <v>46269</v>
+      </c>
+      <c r="I18" s="1">
+        <v>46269</v>
+      </c>
+      <c r="J18" t="str">
         <v>UCS</v>
       </c>
-      <c r="I18">
-        <v>316</v>
-      </c>
-      <c r="J18">
-        <v>316</v>
-      </c>
       <c r="K18" t="str">
         <v/>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="M18">
         <v>0</v>
@@ -1272,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>621</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -1288,53 +882,83 @@
       </c>
       <c r="T18">
         <v>0</v>
+      </c>
+      <c r="U18">
+        <v>0</v>
+      </c>
+      <c r="V18">
+        <v>2240</v>
+      </c>
+      <c r="W18">
+        <v>0</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>0</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+      <c r="AA18">
+        <v>0</v>
+      </c>
+      <c r="AB18">
+        <v>0</v>
+      </c>
+      <c r="AC18">
+        <v>0</v>
+      </c>
+      <c r="AD18">
+        <v>2861</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B19" t="str">
-        <v>T260910000009</v>
+        <v>6909003</v>
+      </c>
+      <c r="B19">
+        <v>5</v>
       </c>
       <c r="C19" t="str">
-        <v>000000024</v>
+        <v>T260904000063</v>
       </c>
       <c r="D19" t="str">
-        <v/>
+        <v>000000002</v>
       </c>
       <c r="E19" t="str">
-        <v>3100000190056</v>
+        <v/>
       </c>
       <c r="F19" t="str">
-        <v>นางทดสอบ24 สมมติ</v>
+        <v>3100000015838</v>
       </c>
       <c r="G19" t="str">
-        <v>10/09/2569</v>
+        <v>นางทดสอบ2 สมมติ</v>
       </c>
       <c r="H19" t="str">
+        <v>04/09/2569</v>
+      </c>
+      <c r="I19" t="str">
+        <v>04/09/2569</v>
+      </c>
+      <c r="J19" t="str">
         <v>UCS</v>
       </c>
-      <c r="I19">
-        <v>653</v>
-      </c>
-      <c r="J19">
-        <v>653</v>
-      </c>
       <c r="K19" t="str">
         <v/>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1051</v>
       </c>
       <c r="M19">
         <v>0</v>
       </c>
       <c r="N19">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>931</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -1350,44 +974,74 @@
       </c>
       <c r="T19">
         <v>0</v>
+      </c>
+      <c r="U19">
+        <v>0</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>0</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+      <c r="AA19">
+        <v>0</v>
+      </c>
+      <c r="AB19">
+        <v>0</v>
+      </c>
+      <c r="AC19">
+        <v>0</v>
+      </c>
+      <c r="AD19">
+        <v>931</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B20" t="str">
-        <v>T260910000039</v>
+        <v>6909001</v>
+      </c>
+      <c r="B20">
+        <v>6</v>
       </c>
       <c r="C20" t="str">
-        <v>000000034</v>
+        <v>T260905000004</v>
       </c>
       <c r="D20" t="str">
-        <v/>
+        <v>000000029</v>
       </c>
       <c r="E20" t="str">
-        <v>3100000269246</v>
+        <v/>
       </c>
       <c r="F20" t="str">
-        <v>นางทดสอบ34 สมมติ</v>
-      </c>
-      <c r="G20" s="1">
-        <v>46275</v>
-      </c>
-      <c r="H20" t="str">
+        <v>3100000229651</v>
+      </c>
+      <c r="G20" t="str">
+        <v>นายทดสอบ29 สมมติ</v>
+      </c>
+      <c r="H20" s="1">
+        <v>46270</v>
+      </c>
+      <c r="I20" s="1">
+        <v>46270</v>
+      </c>
+      <c r="J20" t="str">
         <v>UCS</v>
       </c>
-      <c r="I20">
-        <v>843</v>
-      </c>
-      <c r="J20">
-        <v>843</v>
-      </c>
       <c r="K20" t="str">
         <v/>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="M20">
         <v>0</v>
@@ -1396,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -1411,45 +1065,75 @@
         <v>0</v>
       </c>
       <c r="T20">
-        <v>640</v>
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>348</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B21" t="str">
-        <v>T260910000069</v>
+        <v>6909002</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
       </c>
       <c r="C21" t="str">
-        <v>000000004</v>
+        <v>T260905000034</v>
       </c>
       <c r="D21" t="str">
-        <v/>
+        <v>000000039</v>
       </c>
       <c r="E21" t="str">
-        <v>3100000031676</v>
+        <v/>
       </c>
       <c r="F21" t="str">
-        <v>นางทดสอบ4 สมมติ</v>
+        <v>3100000308841</v>
       </c>
       <c r="G21" t="str">
-        <v>10/09/2569</v>
+        <v>นายทดสอบ39 สมมติ</v>
       </c>
       <c r="H21" t="str">
+        <v>05/09/2569</v>
+      </c>
+      <c r="I21" t="str">
+        <v>05/09/2569</v>
+      </c>
+      <c r="J21" t="str">
         <v>UCS</v>
       </c>
-      <c r="I21">
-        <v>353</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
       <c r="K21" t="str">
-        <v>C438</v>
+        <v/>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>658</v>
       </c>
       <c r="M21">
         <v>0</v>
@@ -1473,45 +1157,75 @@
         <v>0</v>
       </c>
       <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B22" t="str">
-        <v>T260913000012</v>
+        <v>6909003</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
       </c>
       <c r="C22" t="str">
-        <v>000000005</v>
+        <v>T260905000064</v>
       </c>
       <c r="D22" t="str">
-        <v/>
+        <v>000000009</v>
       </c>
       <c r="E22" t="str">
-        <v>3100000039595</v>
+        <v/>
       </c>
       <c r="F22" t="str">
-        <v>นายทดสอบ5 สมมติ</v>
-      </c>
-      <c r="G22" s="1">
-        <v>46278</v>
-      </c>
-      <c r="H22" t="str">
+        <v>3100000071271</v>
+      </c>
+      <c r="G22" t="str">
+        <v>นายทดสอบ9 สมมติ</v>
+      </c>
+      <c r="H22" s="1">
+        <v>46270</v>
+      </c>
+      <c r="I22" s="1">
+        <v>46270</v>
+      </c>
+      <c r="J22" t="str">
         <v>UCS</v>
       </c>
-      <c r="I22">
-        <v>644</v>
-      </c>
-      <c r="J22">
-        <v>644</v>
-      </c>
       <c r="K22" t="str">
         <v/>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="M22">
         <v>0</v>
@@ -1520,7 +1234,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>968</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -1532,48 +1246,78 @@
         <v>0</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="T22">
         <v>0</v>
+      </c>
+      <c r="U22">
+        <v>0</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>0</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+      <c r="AA22">
+        <v>0</v>
+      </c>
+      <c r="AB22">
+        <v>0</v>
+      </c>
+      <c r="AC22">
+        <v>0</v>
+      </c>
+      <c r="AD22">
+        <v>4328</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B23" t="str">
-        <v>T260913000042</v>
+        <v>6909001</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
       </c>
       <c r="C23" t="str">
-        <v>000000015</v>
+        <v>T260908000007</v>
       </c>
       <c r="D23" t="str">
-        <v/>
+        <v>000000010</v>
       </c>
       <c r="E23" t="str">
-        <v>3100000118785</v>
+        <v/>
       </c>
       <c r="F23" t="str">
-        <v>นายทดสอบ15 สมมติ</v>
+        <v>3100000079190</v>
       </c>
       <c r="G23" t="str">
-        <v>13/09/2569</v>
+        <v>นางทดสอบ10 สมมติ</v>
       </c>
       <c r="H23" t="str">
+        <v>08/09/2569</v>
+      </c>
+      <c r="I23" t="str">
+        <v>08/09/2569</v>
+      </c>
+      <c r="J23" t="str">
         <v>UCS</v>
       </c>
-      <c r="I23">
-        <v>954</v>
-      </c>
-      <c r="J23">
-        <v>954</v>
-      </c>
       <c r="K23" t="str">
         <v/>
       </c>
       <c r="L23">
-        <v>2800</v>
+        <v>459</v>
       </c>
       <c r="M23">
         <v>0</v>
@@ -1582,7 +1326,7 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>459</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -1598,53 +1342,83 @@
       </c>
       <c r="T23">
         <v>0</v>
+      </c>
+      <c r="U23">
+        <v>0</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0</v>
+      </c>
+      <c r="X23">
+        <v>0</v>
+      </c>
+      <c r="Y23">
+        <v>0</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+      <c r="AA23">
+        <v>0</v>
+      </c>
+      <c r="AB23">
+        <v>0</v>
+      </c>
+      <c r="AC23">
+        <v>0</v>
+      </c>
+      <c r="AD23">
+        <v>459</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B24" t="str">
-        <v>T260913000072</v>
+        <v>6909002</v>
+      </c>
+      <c r="B24">
+        <v>10</v>
       </c>
       <c r="C24" t="str">
-        <v>000000025</v>
+        <v>T260908000037</v>
       </c>
       <c r="D24" t="str">
-        <v/>
+        <v>000000020</v>
       </c>
       <c r="E24" t="str">
-        <v>3100000197975</v>
+        <v/>
       </c>
       <c r="F24" t="str">
-        <v>นายทดสอบ25 สมมติ</v>
-      </c>
-      <c r="G24" s="1">
-        <v>46278</v>
-      </c>
-      <c r="H24" t="str">
+        <v>3100000158380</v>
+      </c>
+      <c r="G24" t="str">
+        <v>นางทดสอบ20 สมมติ</v>
+      </c>
+      <c r="H24" s="1">
+        <v>46273</v>
+      </c>
+      <c r="I24" s="1">
+        <v>46273</v>
+      </c>
+      <c r="J24" t="str">
         <v>UCS</v>
       </c>
-      <c r="I24">
-        <v>464</v>
-      </c>
-      <c r="J24">
-        <v>464</v>
-      </c>
       <c r="K24" t="str">
         <v/>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="M24">
-        <v>3360</v>
+        <v>0</v>
       </c>
       <c r="N24">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>769</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -1660,44 +1434,74 @@
       </c>
       <c r="T24">
         <v>0</v>
+      </c>
+      <c r="U24">
+        <v>0</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0</v>
+      </c>
+      <c r="X24">
+        <v>0</v>
+      </c>
+      <c r="Y24">
+        <v>0</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+      <c r="AA24">
+        <v>0</v>
+      </c>
+      <c r="AB24">
+        <v>0</v>
+      </c>
+      <c r="AC24">
+        <v>0</v>
+      </c>
+      <c r="AD24">
+        <v>769</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B25" t="str">
-        <v>T260914000013</v>
+        <v>6909003</v>
+      </c>
+      <c r="B25">
+        <v>11</v>
       </c>
       <c r="C25" t="str">
-        <v>000000012</v>
+        <v>T260908000067</v>
       </c>
       <c r="D25" t="str">
-        <v/>
+        <v>000000030</v>
       </c>
       <c r="E25" t="str">
-        <v>3100000095028</v>
+        <v/>
       </c>
       <c r="F25" t="str">
-        <v>นางทดสอบ12 สมมติ</v>
+        <v>3100000237570</v>
       </c>
       <c r="G25" t="str">
-        <v>14/09/2569</v>
+        <v>นางทดสอบ30 สมมติ</v>
       </c>
       <c r="H25" t="str">
+        <v>08/09/2569</v>
+      </c>
+      <c r="I25" t="str">
+        <v>08/09/2569</v>
+      </c>
+      <c r="J25" t="str">
         <v>UCS</v>
       </c>
-      <c r="I25">
-        <v>681</v>
-      </c>
-      <c r="J25">
-        <v>681</v>
-      </c>
       <c r="K25" t="str">
         <v/>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="M25">
         <v>0</v>
@@ -1706,7 +1510,7 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -1722,44 +1526,74 @@
       </c>
       <c r="T25">
         <v>0</v>
+      </c>
+      <c r="U25">
+        <v>0</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0</v>
+      </c>
+      <c r="X25">
+        <v>0</v>
+      </c>
+      <c r="Y25">
+        <v>0</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+      <c r="AA25">
+        <v>0</v>
+      </c>
+      <c r="AB25">
+        <v>0</v>
+      </c>
+      <c r="AC25">
+        <v>0</v>
+      </c>
+      <c r="AD25">
+        <v>279</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B26" t="str">
-        <v>T260914000043</v>
+        <v>6909001</v>
+      </c>
+      <c r="B26">
+        <v>12</v>
       </c>
       <c r="C26" t="str">
-        <v>000000022</v>
+        <v>T260909000008</v>
       </c>
       <c r="D26" t="str">
-        <v/>
+        <v>000000017</v>
       </c>
       <c r="E26" t="str">
-        <v>3100000174218</v>
+        <v/>
       </c>
       <c r="F26" t="str">
-        <v>นางทดสอบ22 สมมติ</v>
-      </c>
-      <c r="G26" s="1">
-        <v>46279</v>
-      </c>
-      <c r="H26" t="str">
+        <v>3100000134623</v>
+      </c>
+      <c r="G26" t="str">
+        <v>นายทดสอบ17 สมมติ</v>
+      </c>
+      <c r="H26" s="1">
+        <v>46274</v>
+      </c>
+      <c r="I26" s="1">
+        <v>46274</v>
+      </c>
+      <c r="J26" t="str">
         <v>UCS</v>
       </c>
-      <c r="I26">
-        <v>991</v>
-      </c>
-      <c r="J26">
-        <v>991</v>
-      </c>
       <c r="K26" t="str">
         <v/>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="M26">
         <v>0</v>
@@ -1768,7 +1602,7 @@
         <v>0</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>496</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -1780,48 +1614,78 @@
         <v>0</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="T26">
         <v>0</v>
+      </c>
+      <c r="U26">
+        <v>0</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0</v>
+      </c>
+      <c r="X26">
+        <v>0</v>
+      </c>
+      <c r="Y26">
+        <v>0</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+      <c r="AA26">
+        <v>0</v>
+      </c>
+      <c r="AB26">
+        <v>0</v>
+      </c>
+      <c r="AC26">
+        <v>0</v>
+      </c>
+      <c r="AD26">
+        <v>3856</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B27" t="str">
-        <v>T260915000014</v>
+        <v>6909003</v>
+      </c>
+      <c r="B27">
+        <v>13</v>
       </c>
       <c r="C27" t="str">
-        <v>000000019</v>
+        <v>T260909000068</v>
       </c>
       <c r="D27" t="str">
-        <v/>
+        <v>000000037</v>
       </c>
       <c r="E27" t="str">
-        <v>3100000150461</v>
+        <v/>
       </c>
       <c r="F27" t="str">
-        <v>นายทดสอบ19 สมมติ</v>
-      </c>
-      <c r="G27" s="1">
-        <v>46280</v>
-      </c>
-      <c r="H27" t="str">
+        <v>3100000293003</v>
+      </c>
+      <c r="G27" t="str">
+        <v>นายทดสอบ37 สมมติ</v>
+      </c>
+      <c r="H27" s="1">
+        <v>46274</v>
+      </c>
+      <c r="I27" s="1">
+        <v>46274</v>
+      </c>
+      <c r="J27" t="str">
         <v>UCS</v>
       </c>
-      <c r="I27">
-        <v>718</v>
-      </c>
-      <c r="J27">
-        <v>718</v>
-      </c>
       <c r="K27" t="str">
         <v/>
       </c>
       <c r="L27">
-        <v>2800</v>
+        <v>316</v>
       </c>
       <c r="M27">
         <v>0</v>
@@ -1830,7 +1694,7 @@
         <v>0</v>
       </c>
       <c r="O27">
-        <v>0</v>
+        <v>316</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -1846,44 +1710,74 @@
       </c>
       <c r="T27">
         <v>0</v>
+      </c>
+      <c r="U27">
+        <v>0</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0</v>
+      </c>
+      <c r="X27">
+        <v>0</v>
+      </c>
+      <c r="Y27">
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+      <c r="AA27">
+        <v>0</v>
+      </c>
+      <c r="AB27">
+        <v>0</v>
+      </c>
+      <c r="AC27">
+        <v>0</v>
+      </c>
+      <c r="AD27">
+        <v>316</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B28" t="str">
-        <v>T260915000044</v>
+        <v>6909001</v>
+      </c>
+      <c r="B28">
+        <v>14</v>
       </c>
       <c r="C28" t="str">
-        <v>000000029</v>
+        <v>T260910000009</v>
       </c>
       <c r="D28" t="str">
-        <v/>
+        <v>000000024</v>
       </c>
       <c r="E28" t="str">
-        <v>3100000229651</v>
+        <v/>
       </c>
       <c r="F28" t="str">
-        <v>นายทดสอบ29 สมมติ</v>
+        <v>3100000190056</v>
       </c>
       <c r="G28" t="str">
-        <v>15/09/2569</v>
+        <v>นางทดสอบ24 สมมติ</v>
       </c>
       <c r="H28" t="str">
+        <v>10/09/2569</v>
+      </c>
+      <c r="I28" t="str">
+        <v>10/09/2569</v>
+      </c>
+      <c r="J28" t="str">
         <v>UCS</v>
       </c>
-      <c r="I28">
-        <v>348</v>
-      </c>
-      <c r="J28">
-        <v>348</v>
-      </c>
       <c r="K28" t="str">
         <v/>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>653</v>
       </c>
       <c r="M28">
         <v>0</v>
@@ -1892,7 +1786,7 @@
         <v>0</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>533</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -1907,45 +1801,75 @@
         <v>0</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="U28">
+        <v>0</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0</v>
+      </c>
+      <c r="X28">
+        <v>0</v>
+      </c>
+      <c r="Y28">
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+      <c r="AA28">
+        <v>0</v>
+      </c>
+      <c r="AB28">
+        <v>0</v>
+      </c>
+      <c r="AC28">
+        <v>0</v>
+      </c>
+      <c r="AD28">
+        <v>773</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B29" t="str">
-        <v>T260915000074</v>
+        <v>6909002</v>
+      </c>
+      <c r="B29">
+        <v>15</v>
       </c>
       <c r="C29" t="str">
-        <v>000000039</v>
+        <v>T260910000039</v>
       </c>
       <c r="D29" t="str">
-        <v/>
+        <v>000000034</v>
       </c>
       <c r="E29" t="str">
-        <v>3100000308841</v>
+        <v/>
       </c>
       <c r="F29" t="str">
-        <v>นายทดสอบ39 สมมติ</v>
-      </c>
-      <c r="G29" s="1">
-        <v>46280</v>
-      </c>
-      <c r="H29" t="str">
+        <v>3100000269246</v>
+      </c>
+      <c r="G29" t="str">
+        <v>นางทดสอบ34 สมมติ</v>
+      </c>
+      <c r="H29" s="1">
+        <v>46275</v>
+      </c>
+      <c r="I29" s="1">
+        <v>46275</v>
+      </c>
+      <c r="J29" t="str">
         <v>UCS</v>
       </c>
-      <c r="I29">
-        <v>538</v>
-      </c>
-      <c r="J29">
-        <v>538</v>
-      </c>
       <c r="K29" t="str">
         <v/>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="M29">
         <v>0</v>
@@ -1954,7 +1878,7 @@
         <v>0</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>843</v>
       </c>
       <c r="P29">
         <v>0</v>
@@ -1970,44 +1894,74 @@
       </c>
       <c r="T29">
         <v>0</v>
+      </c>
+      <c r="U29">
+        <v>0</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0</v>
+      </c>
+      <c r="X29">
+        <v>0</v>
+      </c>
+      <c r="Y29">
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+      <c r="AA29">
+        <v>0</v>
+      </c>
+      <c r="AB29">
+        <v>640</v>
+      </c>
+      <c r="AC29">
+        <v>0</v>
+      </c>
+      <c r="AD29">
+        <v>1483</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B30" t="str">
-        <v>T260915900001</v>
+        <v>6909003</v>
+      </c>
+      <c r="B30">
+        <v>16</v>
       </c>
       <c r="C30" t="str">
-        <v>000000005</v>
+        <v>T260910000069</v>
       </c>
       <c r="D30" t="str">
-        <v/>
+        <v>000000004</v>
       </c>
       <c r="E30" t="str">
-        <v>3100000039595</v>
+        <v/>
       </c>
       <c r="F30" t="str">
-        <v>นายทดสอบ5 สมมติ</v>
+        <v>3100000031676</v>
       </c>
       <c r="G30" t="str">
-        <v>15/09/2569</v>
+        <v>นางทดสอบ4 สมมติ</v>
       </c>
       <c r="H30" t="str">
+        <v>10/09/2569</v>
+      </c>
+      <c r="I30" t="str">
+        <v>10/09/2569</v>
+      </c>
+      <c r="J30" t="str">
         <v>UCS</v>
       </c>
-      <c r="I30">
-        <v>350</v>
-      </c>
-      <c r="J30">
-        <v>0</v>
-      </c>
       <c r="K30" t="str">
-        <v>C438</v>
+        <v/>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>353</v>
       </c>
       <c r="M30">
         <v>0</v>
@@ -2031,45 +1985,75 @@
         <v>0</v>
       </c>
       <c r="T30">
+        <v>0</v>
+      </c>
+      <c r="U30">
+        <v>0</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0</v>
+      </c>
+      <c r="X30">
+        <v>0</v>
+      </c>
+      <c r="Y30">
+        <v>0</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+      <c r="AA30">
+        <v>0</v>
+      </c>
+      <c r="AB30">
+        <v>0</v>
+      </c>
+      <c r="AC30">
+        <v>0</v>
+      </c>
+      <c r="AD30">
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B31" t="str">
-        <v>T260915900002</v>
+        <v>6909001</v>
+      </c>
+      <c r="B31">
+        <v>17</v>
       </c>
       <c r="C31" t="str">
+        <v>T260913000012</v>
+      </c>
+      <c r="D31" t="str">
         <v>000000005</v>
       </c>
-      <c r="D31" t="str">
-        <v/>
-      </c>
       <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
         <v>3100000039595</v>
       </c>
-      <c r="F31" t="str">
+      <c r="G31" t="str">
         <v>นายทดสอบ5 สมมติ</v>
       </c>
-      <c r="G31" s="1">
-        <v>46280</v>
-      </c>
-      <c r="H31" t="str">
+      <c r="H31" s="1">
+        <v>46278</v>
+      </c>
+      <c r="I31" s="1">
+        <v>46278</v>
+      </c>
+      <c r="J31" t="str">
         <v>UCS</v>
       </c>
-      <c r="I31">
-        <v>420</v>
-      </c>
-      <c r="J31">
-        <v>420</v>
-      </c>
       <c r="K31" t="str">
         <v/>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="M31">
         <v>0</v>
@@ -2078,7 +2062,7 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>644</v>
       </c>
       <c r="P31">
         <v>0</v>
@@ -2094,44 +2078,74 @@
       </c>
       <c r="T31">
         <v>0</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0</v>
+      </c>
+      <c r="X31">
+        <v>0</v>
+      </c>
+      <c r="Y31">
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+      <c r="AA31">
+        <v>0</v>
+      </c>
+      <c r="AB31">
+        <v>0</v>
+      </c>
+      <c r="AC31">
+        <v>0</v>
+      </c>
+      <c r="AD31">
+        <v>644</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B32" t="str">
-        <v>T260918000017</v>
+        <v>6909002</v>
+      </c>
+      <c r="B32">
+        <v>18</v>
       </c>
       <c r="C32" t="str">
-        <v>000000040</v>
+        <v>T260913000042</v>
       </c>
       <c r="D32" t="str">
-        <v/>
+        <v>000000015</v>
       </c>
       <c r="E32" t="str">
-        <v>3100000316760</v>
+        <v/>
       </c>
       <c r="F32" t="str">
-        <v>นางทดสอบ40 สมมติ</v>
+        <v>3100000118785</v>
       </c>
       <c r="G32" t="str">
-        <v>18/09/2569</v>
+        <v>นายทดสอบ15 สมมติ</v>
       </c>
       <c r="H32" t="str">
+        <v>13/09/2569</v>
+      </c>
+      <c r="I32" t="str">
+        <v>13/09/2569</v>
+      </c>
+      <c r="J32" t="str">
         <v>UCS</v>
       </c>
-      <c r="I32">
-        <v>829</v>
-      </c>
-      <c r="J32">
-        <v>829</v>
-      </c>
       <c r="K32" t="str">
         <v/>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="M32">
         <v>0</v>
@@ -2140,7 +2154,7 @@
         <v>0</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>954</v>
       </c>
       <c r="P32">
         <v>0</v>
@@ -2149,51 +2163,81 @@
         <v>0</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="S32">
         <v>0</v>
       </c>
       <c r="T32">
         <v>0</v>
+      </c>
+      <c r="U32">
+        <v>0</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0</v>
+      </c>
+      <c r="X32">
+        <v>0</v>
+      </c>
+      <c r="Y32">
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+      <c r="AA32">
+        <v>0</v>
+      </c>
+      <c r="AB32">
+        <v>0</v>
+      </c>
+      <c r="AC32">
+        <v>0</v>
+      </c>
+      <c r="AD32">
+        <v>3754</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B33" t="str">
-        <v>T260918000047</v>
+        <v>6909003</v>
+      </c>
+      <c r="B33">
+        <v>19</v>
       </c>
       <c r="C33" t="str">
-        <v>000000010</v>
+        <v>T260913000072</v>
       </c>
       <c r="D33" t="str">
-        <v/>
+        <v>000000025</v>
       </c>
       <c r="E33" t="str">
-        <v>3100000079190</v>
+        <v/>
       </c>
       <c r="F33" t="str">
-        <v>นางทดสอบ10 สมมติ</v>
-      </c>
-      <c r="G33" s="1">
-        <v>46283</v>
-      </c>
-      <c r="H33" t="str">
+        <v>3100000197975</v>
+      </c>
+      <c r="G33" t="str">
+        <v>นายทดสอบ25 สมมติ</v>
+      </c>
+      <c r="H33" s="1">
+        <v>46278</v>
+      </c>
+      <c r="I33" s="1">
+        <v>46278</v>
+      </c>
+      <c r="J33" t="str">
         <v>UCS</v>
       </c>
-      <c r="I33">
-        <v>339</v>
-      </c>
-      <c r="J33">
-        <v>339</v>
-      </c>
       <c r="K33" t="str">
         <v/>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="M33">
         <v>0</v>
@@ -2202,7 +2246,7 @@
         <v>0</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>464</v>
       </c>
       <c r="P33">
         <v>0</v>
@@ -2214,48 +2258,78 @@
         <v>0</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0</v>
+      </c>
+      <c r="X33">
+        <v>0</v>
+      </c>
+      <c r="Y33">
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+      <c r="AA33">
+        <v>0</v>
+      </c>
+      <c r="AB33">
+        <v>0</v>
+      </c>
+      <c r="AC33">
+        <v>0</v>
+      </c>
+      <c r="AD33">
+        <v>4064</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B34" t="str">
-        <v>T260918000077</v>
+        <v>6909001</v>
+      </c>
+      <c r="B34">
+        <v>20</v>
       </c>
       <c r="C34" t="str">
-        <v>000000020</v>
+        <v>T260914000013</v>
       </c>
       <c r="D34" t="str">
-        <v/>
+        <v>000000012</v>
       </c>
       <c r="E34" t="str">
-        <v>3100000158380</v>
+        <v/>
       </c>
       <c r="F34" t="str">
-        <v>นางทดสอบ20 สมมติ</v>
+        <v>3100000095028</v>
       </c>
       <c r="G34" t="str">
-        <v>18/09/2569</v>
+        <v>นางทดสอบ12 สมมติ</v>
       </c>
       <c r="H34" t="str">
+        <v>14/09/2569</v>
+      </c>
+      <c r="I34" t="str">
+        <v>14/09/2569</v>
+      </c>
+      <c r="J34" t="str">
         <v>UCS</v>
       </c>
-      <c r="I34">
-        <v>649</v>
-      </c>
-      <c r="J34">
-        <v>649</v>
-      </c>
       <c r="K34" t="str">
         <v/>
       </c>
       <c r="L34">
-        <v>2800</v>
+        <v>681</v>
       </c>
       <c r="M34">
         <v>0</v>
@@ -2264,10 +2338,10 @@
         <v>0</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>681</v>
       </c>
       <c r="P34">
-        <v>2240</v>
+        <v>0</v>
       </c>
       <c r="Q34">
         <v>0</v>
@@ -2280,53 +2354,83 @@
       </c>
       <c r="T34">
         <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>0</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>0</v>
+      </c>
+      <c r="AC34">
+        <v>0</v>
+      </c>
+      <c r="AD34">
+        <v>681</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B35" t="str">
-        <v>T260919000018</v>
+        <v>6909002</v>
+      </c>
+      <c r="B35">
+        <v>21</v>
       </c>
       <c r="C35" t="str">
-        <v>000000007</v>
+        <v>T260914000043</v>
       </c>
       <c r="D35" t="str">
-        <v/>
+        <v>000000022</v>
       </c>
       <c r="E35" t="str">
-        <v>3100000055433</v>
+        <v/>
       </c>
       <c r="F35" t="str">
-        <v>นายทดสอบ7 สมมติ</v>
-      </c>
-      <c r="G35" s="1">
-        <v>46284</v>
-      </c>
-      <c r="H35" t="str">
+        <v>3100000174218</v>
+      </c>
+      <c r="G35" t="str">
+        <v>นางทดสอบ22 สมมติ</v>
+      </c>
+      <c r="H35" s="1">
+        <v>46279</v>
+      </c>
+      <c r="I35" s="1">
+        <v>46279</v>
+      </c>
+      <c r="J35" t="str">
         <v>UCS</v>
       </c>
-      <c r="I35">
-        <v>866</v>
-      </c>
-      <c r="J35">
-        <v>866</v>
-      </c>
       <c r="K35" t="str">
         <v/>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="M35">
         <v>0</v>
       </c>
       <c r="N35">
-        <v>240</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>991</v>
       </c>
       <c r="P35">
         <v>0</v>
@@ -2342,44 +2446,74 @@
       </c>
       <c r="T35">
         <v>0</v>
+      </c>
+      <c r="U35">
+        <v>0</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0</v>
+      </c>
+      <c r="X35">
+        <v>0</v>
+      </c>
+      <c r="Y35">
+        <v>0</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+      <c r="AA35">
+        <v>0</v>
+      </c>
+      <c r="AB35">
+        <v>0</v>
+      </c>
+      <c r="AC35">
+        <v>0</v>
+      </c>
+      <c r="AD35">
+        <v>991</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B36" t="str">
-        <v>T260919000078</v>
+        <v>6909001</v>
+      </c>
+      <c r="B36">
+        <v>22</v>
       </c>
       <c r="C36" t="str">
-        <v>000000027</v>
+        <v>T260915000014</v>
       </c>
       <c r="D36" t="str">
-        <v/>
+        <v>000000019</v>
       </c>
       <c r="E36" t="str">
-        <v>3100000213813</v>
+        <v/>
       </c>
       <c r="F36" t="str">
-        <v>นายทดสอบ27 สมมติ</v>
-      </c>
-      <c r="G36" s="1">
-        <v>46284</v>
-      </c>
-      <c r="H36" t="str">
+        <v>3100000150461</v>
+      </c>
+      <c r="G36" t="str">
+        <v>นายทดสอบ19 สมมติ</v>
+      </c>
+      <c r="H36" s="1">
+        <v>46280</v>
+      </c>
+      <c r="I36" s="1">
+        <v>46280</v>
+      </c>
+      <c r="J36" t="str">
         <v>UCS</v>
       </c>
-      <c r="I36">
-        <v>686</v>
-      </c>
-      <c r="J36">
-        <v>686</v>
-      </c>
       <c r="K36" t="str">
         <v/>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>718</v>
       </c>
       <c r="M36">
         <v>0</v>
@@ -2388,7 +2522,7 @@
         <v>0</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>718</v>
       </c>
       <c r="P36">
         <v>0</v>
@@ -2397,51 +2531,81 @@
         <v>0</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="S36">
         <v>0</v>
       </c>
       <c r="T36">
-        <v>640</v>
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>3518</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B37" t="str">
-        <v>T260920000019</v>
+        <v>6909002</v>
+      </c>
+      <c r="B37">
+        <v>23</v>
       </c>
       <c r="C37" t="str">
-        <v>000000014</v>
+        <v>T260915000044</v>
       </c>
       <c r="D37" t="str">
-        <v/>
+        <v>000000029</v>
       </c>
       <c r="E37" t="str">
-        <v>3100000110866</v>
+        <v/>
       </c>
       <c r="F37" t="str">
-        <v>นางทดสอบ14 สมมติ</v>
+        <v>3100000229651</v>
       </c>
       <c r="G37" t="str">
-        <v>20/09/2569</v>
+        <v>นายทดสอบ29 สมมติ</v>
       </c>
       <c r="H37" t="str">
+        <v>15/09/2569</v>
+      </c>
+      <c r="I37" t="str">
+        <v>15/09/2569</v>
+      </c>
+      <c r="J37" t="str">
         <v>UCS</v>
       </c>
-      <c r="I37">
-        <v>1023</v>
-      </c>
-      <c r="J37">
-        <v>1023</v>
-      </c>
       <c r="K37" t="str">
         <v/>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>348</v>
       </c>
       <c r="M37">
         <v>0</v>
@@ -2450,7 +2614,7 @@
         <v>0</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>228</v>
       </c>
       <c r="P37">
         <v>0</v>
@@ -2466,44 +2630,74 @@
       </c>
       <c r="T37">
         <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>228</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B38" t="str">
-        <v>T260920000049</v>
+        <v>6909003</v>
+      </c>
+      <c r="B38">
+        <v>24</v>
       </c>
       <c r="C38" t="str">
-        <v>000000024</v>
+        <v>T260915000074</v>
       </c>
       <c r="D38" t="str">
-        <v/>
+        <v>000000039</v>
       </c>
       <c r="E38" t="str">
-        <v>3100000190056</v>
+        <v/>
       </c>
       <c r="F38" t="str">
-        <v>นางทดสอบ24 สมมติ</v>
-      </c>
-      <c r="G38" s="1">
-        <v>46285</v>
-      </c>
-      <c r="H38" t="str">
+        <v>3100000308841</v>
+      </c>
+      <c r="G38" t="str">
+        <v>นายทดสอบ39 สมมติ</v>
+      </c>
+      <c r="H38" s="1">
+        <v>46280</v>
+      </c>
+      <c r="I38" s="1">
+        <v>46280</v>
+      </c>
+      <c r="J38" t="str">
         <v>UCS</v>
       </c>
-      <c r="I38">
-        <v>413</v>
-      </c>
-      <c r="J38">
-        <v>413</v>
-      </c>
       <c r="K38" t="str">
         <v/>
       </c>
       <c r="L38">
-        <v>2800</v>
+        <v>538</v>
       </c>
       <c r="M38">
         <v>0</v>
@@ -2512,7 +2706,7 @@
         <v>0</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>538</v>
       </c>
       <c r="P38">
         <v>0</v>
@@ -2528,44 +2722,74 @@
       </c>
       <c r="T38">
         <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>538</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B39" t="str">
-        <v>T260920000079</v>
+        <v>6909001</v>
+      </c>
+      <c r="B39">
+        <v>25</v>
       </c>
       <c r="C39" t="str">
-        <v>000000034</v>
+        <v>T260915900001</v>
       </c>
       <c r="D39" t="str">
-        <v/>
+        <v>000000005</v>
       </c>
       <c r="E39" t="str">
-        <v>3100000269246</v>
+        <v/>
       </c>
       <c r="F39" t="str">
-        <v>นางทดสอบ34 สมมติ</v>
+        <v>3100000039595</v>
       </c>
       <c r="G39" t="str">
-        <v>20/09/2569</v>
+        <v>นายทดสอบ5 สมมติ</v>
       </c>
       <c r="H39" t="str">
+        <v>15/09/2569</v>
+      </c>
+      <c r="I39" t="str">
+        <v>15/09/2569</v>
+      </c>
+      <c r="J39" t="str">
         <v>UCS</v>
       </c>
-      <c r="I39">
-        <v>723</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
       <c r="K39" t="str">
-        <v>C438</v>
+        <v/>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="M39">
         <v>0</v>
@@ -2589,45 +2813,75 @@
         <v>0</v>
       </c>
       <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
         <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B40" t="str">
-        <v>T260923000022</v>
+        <v>6909002</v>
+      </c>
+      <c r="B40">
+        <v>26</v>
       </c>
       <c r="C40" t="str">
-        <v>000000035</v>
+        <v>T260915900002</v>
       </c>
       <c r="D40" t="str">
-        <v/>
+        <v>000000005</v>
       </c>
       <c r="E40" t="str">
-        <v>3100000277165</v>
+        <v/>
       </c>
       <c r="F40" t="str">
-        <v>นายทดสอบ35 สมมติ</v>
-      </c>
-      <c r="G40" s="1">
-        <v>46288</v>
-      </c>
-      <c r="H40" t="str">
+        <v>3100000039595</v>
+      </c>
+      <c r="G40" t="str">
+        <v>นายทดสอบ5 สมมติ</v>
+      </c>
+      <c r="H40" s="1">
+        <v>46280</v>
+      </c>
+      <c r="I40" s="1">
+        <v>46280</v>
+      </c>
+      <c r="J40" t="str">
         <v>UCS</v>
       </c>
-      <c r="I40">
-        <v>214</v>
-      </c>
-      <c r="J40">
-        <v>214</v>
-      </c>
       <c r="K40" t="str">
         <v/>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="M40">
         <v>0</v>
@@ -2636,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="P40">
-        <v>2240</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <v>0</v>
@@ -2652,44 +2906,74 @@
       </c>
       <c r="T40">
         <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>420</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B41" t="str">
-        <v>T260923000052</v>
+        <v>6909003</v>
+      </c>
+      <c r="B41">
+        <v>27</v>
       </c>
       <c r="C41" t="str">
-        <v>000000005</v>
+        <v>T260918000017</v>
       </c>
       <c r="D41" t="str">
-        <v/>
+        <v>000000040</v>
       </c>
       <c r="E41" t="str">
-        <v>3100000039595</v>
+        <v/>
       </c>
       <c r="F41" t="str">
-        <v>นายทดสอบ5 สมมติ</v>
+        <v>3100000316760</v>
       </c>
       <c r="G41" t="str">
-        <v>23/09/2569</v>
+        <v>นางทดสอบ40 สมมติ</v>
       </c>
       <c r="H41" t="str">
+        <v>18/09/2569</v>
+      </c>
+      <c r="I41" t="str">
+        <v>18/09/2569</v>
+      </c>
+      <c r="J41" t="str">
         <v>UCS</v>
       </c>
-      <c r="I41">
-        <v>524</v>
-      </c>
-      <c r="J41">
-        <v>524</v>
-      </c>
       <c r="K41" t="str">
         <v/>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="M41">
         <v>0</v>
@@ -2698,7 +2982,7 @@
         <v>0</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="P41">
         <v>0</v>
@@ -2713,45 +2997,75 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>640</v>
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>829</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B42" t="str">
-        <v>T260923000082</v>
+        <v>6909001</v>
+      </c>
+      <c r="B42">
+        <v>28</v>
       </c>
       <c r="C42" t="str">
-        <v>000000015</v>
+        <v>T260918000047</v>
       </c>
       <c r="D42" t="str">
-        <v/>
+        <v>000000010</v>
       </c>
       <c r="E42" t="str">
-        <v>3100000118785</v>
+        <v/>
       </c>
       <c r="F42" t="str">
-        <v>นายทดสอบ15 สมมติ</v>
-      </c>
-      <c r="G42" s="1">
-        <v>46288</v>
-      </c>
-      <c r="H42" t="str">
+        <v>3100000079190</v>
+      </c>
+      <c r="G42" t="str">
+        <v>นางทดสอบ10 สมมติ</v>
+      </c>
+      <c r="H42" s="1">
+        <v>46283</v>
+      </c>
+      <c r="I42" s="1">
+        <v>46283</v>
+      </c>
+      <c r="J42" t="str">
         <v>UCS</v>
       </c>
-      <c r="I42">
-        <v>834</v>
-      </c>
-      <c r="J42">
-        <v>834</v>
-      </c>
       <c r="K42" t="str">
         <v/>
       </c>
       <c r="L42">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="M42">
         <v>0</v>
@@ -2760,7 +3074,7 @@
         <v>0</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="P42">
         <v>0</v>
@@ -2776,44 +3090,74 @@
       </c>
       <c r="T42">
         <v>0</v>
+      </c>
+      <c r="U42">
+        <v>0</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>0</v>
+      </c>
+      <c r="Y42">
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+      <c r="AA42">
+        <v>0</v>
+      </c>
+      <c r="AB42">
+        <v>0</v>
+      </c>
+      <c r="AC42">
+        <v>0</v>
+      </c>
+      <c r="AD42">
+        <v>339</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B43" t="str">
-        <v>T260924000023</v>
+        <v>6909002</v>
+      </c>
+      <c r="B43">
+        <v>29</v>
       </c>
       <c r="C43" t="str">
-        <v>000000002</v>
+        <v>T260918000077</v>
       </c>
       <c r="D43" t="str">
-        <v/>
+        <v>000000020</v>
       </c>
       <c r="E43" t="str">
-        <v>3100000015838</v>
+        <v/>
       </c>
       <c r="F43" t="str">
-        <v>นางทดสอบ2 สมมติ</v>
+        <v>3100000158380</v>
       </c>
       <c r="G43" t="str">
-        <v>24/09/2569</v>
+        <v>นางทดสอบ20 สมมติ</v>
       </c>
       <c r="H43" t="str">
+        <v>18/09/2569</v>
+      </c>
+      <c r="I43" t="str">
+        <v>18/09/2569</v>
+      </c>
+      <c r="J43" t="str">
         <v>UCS</v>
       </c>
-      <c r="I43">
-        <v>251</v>
-      </c>
-      <c r="J43">
-        <v>251</v>
-      </c>
       <c r="K43" t="str">
         <v/>
       </c>
       <c r="L43">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="M43">
         <v>0</v>
@@ -2822,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>649</v>
       </c>
       <c r="P43">
         <v>0</v>
@@ -2831,51 +3175,81 @@
         <v>0</v>
       </c>
       <c r="R43">
-        <v>0</v>
+        <v>2800</v>
       </c>
       <c r="S43">
         <v>0</v>
       </c>
       <c r="T43">
         <v>0</v>
+      </c>
+      <c r="U43">
+        <v>0</v>
+      </c>
+      <c r="V43">
+        <v>2240</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>0</v>
+      </c>
+      <c r="Y43">
+        <v>0</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+      <c r="AA43">
+        <v>0</v>
+      </c>
+      <c r="AB43">
+        <v>0</v>
+      </c>
+      <c r="AC43">
+        <v>0</v>
+      </c>
+      <c r="AD43">
+        <v>5689</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B44" t="str">
-        <v>T260924000053</v>
+        <v>6909003</v>
+      </c>
+      <c r="B44">
+        <v>30</v>
       </c>
       <c r="C44" t="str">
-        <v>000000012</v>
+        <v>T260919000018</v>
       </c>
       <c r="D44" t="str">
-        <v/>
+        <v>000000007</v>
       </c>
       <c r="E44" t="str">
-        <v>3100000095028</v>
+        <v/>
       </c>
       <c r="F44" t="str">
-        <v>นางทดสอบ12 สมมติ</v>
-      </c>
-      <c r="G44" s="1">
-        <v>46289</v>
-      </c>
-      <c r="H44" t="str">
+        <v>3100000055433</v>
+      </c>
+      <c r="G44" t="str">
+        <v>นายทดสอบ7 สมมติ</v>
+      </c>
+      <c r="H44" s="1">
+        <v>46284</v>
+      </c>
+      <c r="I44" s="1">
+        <v>46284</v>
+      </c>
+      <c r="J44" t="str">
         <v>UCS</v>
       </c>
-      <c r="I44">
-        <v>561</v>
-      </c>
-      <c r="J44">
-        <v>561</v>
-      </c>
       <c r="K44" t="str">
         <v/>
       </c>
       <c r="L44">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="M44">
         <v>0</v>
@@ -2884,7 +3258,7 @@
         <v>0</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>866</v>
       </c>
       <c r="P44">
         <v>0</v>
@@ -2899,54 +3273,84 @@
         <v>0</v>
       </c>
       <c r="T44">
-        <v>0</v>
+        <v>240</v>
+      </c>
+      <c r="U44">
+        <v>0</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>0</v>
+      </c>
+      <c r="Y44">
+        <v>0</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+      <c r="AA44">
+        <v>0</v>
+      </c>
+      <c r="AB44">
+        <v>0</v>
+      </c>
+      <c r="AC44">
+        <v>0</v>
+      </c>
+      <c r="AD44">
+        <v>1106</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B45" t="str">
-        <v>T260925000024</v>
+        <v>6909002</v>
+      </c>
+      <c r="B45">
+        <v>31</v>
       </c>
       <c r="C45" t="str">
-        <v>000000009</v>
+        <v>T260919000078</v>
       </c>
       <c r="D45" t="str">
-        <v/>
+        <v>000000027</v>
       </c>
       <c r="E45" t="str">
-        <v>3100000071271</v>
+        <v/>
       </c>
       <c r="F45" t="str">
-        <v>นายทดสอบ9 สมมติ</v>
-      </c>
-      <c r="G45" s="1">
-        <v>46290</v>
-      </c>
-      <c r="H45" t="str">
+        <v>3100000213813</v>
+      </c>
+      <c r="G45" t="str">
+        <v>นายทดสอบ27 สมมติ</v>
+      </c>
+      <c r="H45" s="1">
+        <v>46284</v>
+      </c>
+      <c r="I45" s="1">
+        <v>46284</v>
+      </c>
+      <c r="J45" t="str">
         <v>UCS</v>
       </c>
-      <c r="I45">
-        <v>288</v>
-      </c>
-      <c r="J45">
-        <v>288</v>
-      </c>
       <c r="K45" t="str">
         <v/>
       </c>
       <c r="L45">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="M45">
-        <v>3360</v>
+        <v>0</v>
       </c>
       <c r="N45">
         <v>0</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>686</v>
       </c>
       <c r="P45">
         <v>0</v>
@@ -2962,44 +3366,74 @@
       </c>
       <c r="T45">
         <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>640</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>1326</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B46" t="str">
-        <v>T260925000054</v>
+        <v>6909003</v>
+      </c>
+      <c r="B46">
+        <v>32</v>
       </c>
       <c r="C46" t="str">
-        <v>000000019</v>
+        <v>T260920000019</v>
       </c>
       <c r="D46" t="str">
-        <v/>
+        <v>000000014</v>
       </c>
       <c r="E46" t="str">
-        <v>3100000150461</v>
+        <v/>
       </c>
       <c r="F46" t="str">
-        <v>นายทดสอบ19 สมมติ</v>
+        <v>3100000110866</v>
       </c>
       <c r="G46" t="str">
-        <v>25/09/2569</v>
+        <v>นางทดสอบ14 สมมติ</v>
       </c>
       <c r="H46" t="str">
+        <v>20/09/2569</v>
+      </c>
+      <c r="I46" t="str">
+        <v>20/09/2569</v>
+      </c>
+      <c r="J46" t="str">
         <v>UCS</v>
       </c>
-      <c r="I46">
-        <v>718</v>
-      </c>
-      <c r="J46">
-        <v>718</v>
-      </c>
       <c r="K46" t="str">
         <v/>
       </c>
       <c r="L46">
-        <v>0</v>
+        <v>1023</v>
       </c>
       <c r="M46">
         <v>0</v>
@@ -3008,7 +3442,7 @@
         <v>0</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>903</v>
       </c>
       <c r="P46">
         <v>0</v>
@@ -3024,106 +3458,166 @@
       </c>
       <c r="T46">
         <v>0</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>0</v>
+      </c>
+      <c r="Y46">
+        <v>0</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+      <c r="AA46">
+        <v>0</v>
+      </c>
+      <c r="AB46">
+        <v>0</v>
+      </c>
+      <c r="AC46">
+        <v>0</v>
+      </c>
+      <c r="AD46">
+        <v>903</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B47" t="str">
-        <v>T260925000084</v>
+        <v>6909001</v>
+      </c>
+      <c r="B47">
+        <v>33</v>
       </c>
       <c r="C47" t="str">
-        <v>000000029</v>
+        <v>T260920000049</v>
       </c>
       <c r="D47" t="str">
-        <v/>
+        <v>000000024</v>
       </c>
       <c r="E47" t="str">
-        <v>3100000229651</v>
+        <v/>
       </c>
       <c r="F47" t="str">
-        <v>นายทดสอบ29 สมมติ</v>
-      </c>
-      <c r="G47" s="1">
-        <v>46290</v>
-      </c>
-      <c r="H47" t="str">
+        <v>3100000190056</v>
+      </c>
+      <c r="G47" t="str">
+        <v>นางทดสอบ24 สมมติ</v>
+      </c>
+      <c r="H47" s="1">
+        <v>46285</v>
+      </c>
+      <c r="I47" s="1">
+        <v>46285</v>
+      </c>
+      <c r="J47" t="str">
         <v>UCS</v>
       </c>
-      <c r="I47">
-        <v>908</v>
-      </c>
-      <c r="J47">
-        <v>908</v>
-      </c>
       <c r="K47" t="str">
         <v/>
       </c>
       <c r="L47">
+        <v>413</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>413</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+      <c r="Q47">
+        <v>0</v>
+      </c>
+      <c r="R47">
         <v>2800</v>
       </c>
-      <c r="M47">
-        <v>0</v>
-      </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
-      <c r="O47">
-        <v>0</v>
-      </c>
-      <c r="P47">
-        <v>0</v>
-      </c>
-      <c r="Q47">
-        <v>0</v>
-      </c>
-      <c r="R47">
-        <v>0</v>
-      </c>
       <c r="S47">
         <v>0</v>
       </c>
       <c r="T47">
         <v>0</v>
+      </c>
+      <c r="U47">
+        <v>0</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>0</v>
+      </c>
+      <c r="Y47">
+        <v>0</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+      <c r="AA47">
+        <v>0</v>
+      </c>
+      <c r="AB47">
+        <v>0</v>
+      </c>
+      <c r="AC47">
+        <v>0</v>
+      </c>
+      <c r="AD47">
+        <v>3213</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B48" t="str">
-        <v>T260928000027</v>
+        <v>6909002</v>
+      </c>
+      <c r="B48">
+        <v>34</v>
       </c>
       <c r="C48" t="str">
-        <v>000000030</v>
+        <v>T260920000079</v>
       </c>
       <c r="D48" t="str">
-        <v/>
+        <v>000000034</v>
       </c>
       <c r="E48" t="str">
-        <v>3100000237570</v>
+        <v/>
       </c>
       <c r="F48" t="str">
-        <v>นางทดสอบ30 สมมติ</v>
+        <v>3100000269246</v>
       </c>
       <c r="G48" t="str">
-        <v>28/09/2569</v>
+        <v>นางทดสอบ34 สมมติ</v>
       </c>
       <c r="H48" t="str">
+        <v>20/09/2569</v>
+      </c>
+      <c r="I48" t="str">
+        <v>20/09/2569</v>
+      </c>
+      <c r="J48" t="str">
         <v>UCS</v>
       </c>
-      <c r="I48">
-        <v>399</v>
-      </c>
-      <c r="J48">
-        <v>0</v>
-      </c>
       <c r="K48" t="str">
-        <v>C438</v>
+        <v/>
       </c>
       <c r="L48">
-        <v>0</v>
+        <v>723</v>
       </c>
       <c r="M48">
         <v>0</v>
@@ -3147,45 +3641,75 @@
         <v>0</v>
       </c>
       <c r="T48">
+        <v>0</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0</v>
+      </c>
+      <c r="X48">
+        <v>0</v>
+      </c>
+      <c r="Y48">
+        <v>0</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+      <c r="AA48">
+        <v>0</v>
+      </c>
+      <c r="AB48">
+        <v>0</v>
+      </c>
+      <c r="AC48">
+        <v>0</v>
+      </c>
+      <c r="AD48">
         <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B49" t="str">
-        <v>T260928000057</v>
+        <v>6909003</v>
+      </c>
+      <c r="B49">
+        <v>35</v>
       </c>
       <c r="C49" t="str">
-        <v>000000040</v>
+        <v>T260923000022</v>
       </c>
       <c r="D49" t="str">
-        <v/>
+        <v>000000035</v>
       </c>
       <c r="E49" t="str">
-        <v>3100000316760</v>
+        <v/>
       </c>
       <c r="F49" t="str">
-        <v>นางทดสอบ40 สมมติ</v>
-      </c>
-      <c r="G49" s="1">
-        <v>46293</v>
-      </c>
-      <c r="H49" t="str">
+        <v>3100000277165</v>
+      </c>
+      <c r="G49" t="str">
+        <v>นายทดสอบ35 สมมติ</v>
+      </c>
+      <c r="H49" s="1">
+        <v>46288</v>
+      </c>
+      <c r="I49" s="1">
+        <v>46288</v>
+      </c>
+      <c r="J49" t="str">
         <v>UCS</v>
       </c>
-      <c r="I49">
-        <v>709</v>
-      </c>
-      <c r="J49">
-        <v>709</v>
-      </c>
       <c r="K49" t="str">
         <v/>
       </c>
       <c r="L49">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="M49">
         <v>0</v>
@@ -3194,7 +3718,7 @@
         <v>0</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="P49">
         <v>0</v>
@@ -3210,44 +3734,74 @@
       </c>
       <c r="T49">
         <v>0</v>
+      </c>
+      <c r="U49">
+        <v>0</v>
+      </c>
+      <c r="V49">
+        <v>2240</v>
+      </c>
+      <c r="W49">
+        <v>0</v>
+      </c>
+      <c r="X49">
+        <v>0</v>
+      </c>
+      <c r="Y49">
+        <v>0</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+      <c r="AA49">
+        <v>0</v>
+      </c>
+      <c r="AB49">
+        <v>0</v>
+      </c>
+      <c r="AC49">
+        <v>0</v>
+      </c>
+      <c r="AD49">
+        <v>2454</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B50" t="str">
-        <v>T260928000087</v>
+        <v>6909001</v>
+      </c>
+      <c r="B50">
+        <v>36</v>
       </c>
       <c r="C50" t="str">
-        <v>000000010</v>
+        <v>T260923000052</v>
       </c>
       <c r="D50" t="str">
-        <v/>
+        <v>000000005</v>
       </c>
       <c r="E50" t="str">
-        <v>3100000079190</v>
+        <v/>
       </c>
       <c r="F50" t="str">
-        <v>นางทดสอบ10 สมมติ</v>
+        <v>3100000039595</v>
       </c>
       <c r="G50" t="str">
-        <v>28/09/2569</v>
+        <v>นายทดสอบ5 สมมติ</v>
       </c>
       <c r="H50" t="str">
+        <v>23/09/2569</v>
+      </c>
+      <c r="I50" t="str">
+        <v>23/09/2569</v>
+      </c>
+      <c r="J50" t="str">
         <v>UCS</v>
       </c>
-      <c r="I50">
-        <v>219</v>
-      </c>
-      <c r="J50">
-        <v>219</v>
-      </c>
       <c r="K50" t="str">
         <v/>
       </c>
       <c r="L50">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="M50">
         <v>0</v>
@@ -3256,7 +3810,7 @@
         <v>0</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>524</v>
       </c>
       <c r="P50">
         <v>0</v>
@@ -3272,44 +3826,74 @@
       </c>
       <c r="T50">
         <v>0</v>
+      </c>
+      <c r="U50">
+        <v>0</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0</v>
+      </c>
+      <c r="X50">
+        <v>0</v>
+      </c>
+      <c r="Y50">
+        <v>0</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+      <c r="AA50">
+        <v>0</v>
+      </c>
+      <c r="AB50">
+        <v>640</v>
+      </c>
+      <c r="AC50">
+        <v>0</v>
+      </c>
+      <c r="AD50">
+        <v>1164</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>6909003</v>
-      </c>
-      <c r="B51" t="str">
-        <v>T260929000028</v>
+        <v>6909002</v>
+      </c>
+      <c r="B51">
+        <v>37</v>
       </c>
       <c r="C51" t="str">
-        <v>000000037</v>
+        <v>T260923000082</v>
       </c>
       <c r="D51" t="str">
-        <v/>
+        <v>000000015</v>
       </c>
       <c r="E51" t="str">
-        <v>3100000293003</v>
+        <v/>
       </c>
       <c r="F51" t="str">
-        <v>นายทดสอบ37 สมมติ</v>
-      </c>
-      <c r="G51" s="1">
-        <v>46294</v>
-      </c>
-      <c r="H51" t="str">
+        <v>3100000118785</v>
+      </c>
+      <c r="G51" t="str">
+        <v>นายทดสอบ15 สมมติ</v>
+      </c>
+      <c r="H51" s="1">
+        <v>46288</v>
+      </c>
+      <c r="I51" s="1">
+        <v>46288</v>
+      </c>
+      <c r="J51" t="str">
         <v>UCS</v>
       </c>
-      <c r="I51">
-        <v>436</v>
-      </c>
-      <c r="J51">
-        <v>436</v>
-      </c>
       <c r="K51" t="str">
         <v/>
       </c>
       <c r="L51">
-        <v>2800</v>
+        <v>834</v>
       </c>
       <c r="M51">
         <v>0</v>
@@ -3318,7 +3902,7 @@
         <v>0</v>
       </c>
       <c r="O51">
-        <v>0</v>
+        <v>834</v>
       </c>
       <c r="P51">
         <v>0</v>
@@ -3334,44 +3918,74 @@
       </c>
       <c r="T51">
         <v>0</v>
+      </c>
+      <c r="U51">
+        <v>0</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0</v>
+      </c>
+      <c r="X51">
+        <v>0</v>
+      </c>
+      <c r="Y51">
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+      <c r="AA51">
+        <v>0</v>
+      </c>
+      <c r="AB51">
+        <v>0</v>
+      </c>
+      <c r="AC51">
+        <v>0</v>
+      </c>
+      <c r="AD51">
+        <v>834</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B52" t="str">
-        <v>T260929000058</v>
+        <v>6909003</v>
+      </c>
+      <c r="B52">
+        <v>38</v>
       </c>
       <c r="C52" t="str">
-        <v>000000007</v>
+        <v>T260924000023</v>
       </c>
       <c r="D52" t="str">
-        <v/>
+        <v>000000002</v>
       </c>
       <c r="E52" t="str">
-        <v>3100000055433</v>
+        <v/>
       </c>
       <c r="F52" t="str">
-        <v>นายทดสอบ7 สมมติ</v>
+        <v>3100000015838</v>
       </c>
       <c r="G52" t="str">
-        <v>29/09/2569</v>
+        <v>นางทดสอบ2 สมมติ</v>
       </c>
       <c r="H52" t="str">
+        <v>24/09/2569</v>
+      </c>
+      <c r="I52" t="str">
+        <v>24/09/2569</v>
+      </c>
+      <c r="J52" t="str">
         <v>UCS</v>
       </c>
-      <c r="I52">
-        <v>746</v>
-      </c>
-      <c r="J52">
-        <v>746</v>
-      </c>
       <c r="K52" t="str">
         <v/>
       </c>
       <c r="L52">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="M52">
         <v>0</v>
@@ -3380,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="P52">
         <v>0</v>
@@ -3396,56 +4010,86 @@
       </c>
       <c r="T52">
         <v>0</v>
+      </c>
+      <c r="U52">
+        <v>0</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0</v>
+      </c>
+      <c r="X52">
+        <v>0</v>
+      </c>
+      <c r="Y52">
+        <v>0</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+      <c r="AA52">
+        <v>0</v>
+      </c>
+      <c r="AB52">
+        <v>0</v>
+      </c>
+      <c r="AC52">
+        <v>0</v>
+      </c>
+      <c r="AD52">
+        <v>251</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B53" t="str">
-        <v>T260929000088</v>
+        <v>6909001</v>
+      </c>
+      <c r="B53">
+        <v>39</v>
       </c>
       <c r="C53" t="str">
-        <v>000000017</v>
+        <v>T260924000053</v>
       </c>
       <c r="D53" t="str">
-        <v/>
+        <v>000000012</v>
       </c>
       <c r="E53" t="str">
-        <v>3100000134623</v>
+        <v/>
       </c>
       <c r="F53" t="str">
-        <v>นายทดสอบ17 สมมติ</v>
-      </c>
-      <c r="G53" s="1">
-        <v>46294</v>
-      </c>
-      <c r="H53" t="str">
+        <v>3100000095028</v>
+      </c>
+      <c r="G53" t="str">
+        <v>นางทดสอบ12 สมมติ</v>
+      </c>
+      <c r="H53" s="1">
+        <v>46289</v>
+      </c>
+      <c r="I53" s="1">
+        <v>46289</v>
+      </c>
+      <c r="J53" t="str">
         <v>UCS</v>
       </c>
-      <c r="I53">
-        <v>256</v>
-      </c>
-      <c r="J53">
-        <v>256</v>
-      </c>
       <c r="K53" t="str">
         <v/>
       </c>
       <c r="L53">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="M53">
-        <v>3360</v>
+        <v>0</v>
       </c>
       <c r="N53">
         <v>0</v>
       </c>
       <c r="O53">
-        <v>0</v>
+        <v>561</v>
       </c>
       <c r="P53">
-        <v>2240</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <v>0</v>
@@ -3458,44 +4102,74 @@
       </c>
       <c r="T53">
         <v>0</v>
+      </c>
+      <c r="U53">
+        <v>0</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0</v>
+      </c>
+      <c r="X53">
+        <v>0</v>
+      </c>
+      <c r="Y53">
+        <v>0</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+      <c r="AA53">
+        <v>0</v>
+      </c>
+      <c r="AB53">
+        <v>0</v>
+      </c>
+      <c r="AC53">
+        <v>0</v>
+      </c>
+      <c r="AD53">
+        <v>561</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B54" t="str">
-        <v>T260930000059</v>
+        <v>6909003</v>
+      </c>
+      <c r="B54">
+        <v>40</v>
       </c>
       <c r="C54" t="str">
-        <v>000000014</v>
+        <v>T260925000024</v>
       </c>
       <c r="D54" t="str">
-        <v/>
+        <v>000000009</v>
       </c>
       <c r="E54" t="str">
-        <v>3100000110866</v>
+        <v/>
       </c>
       <c r="F54" t="str">
-        <v>นางทดสอบ14 สมมติ</v>
-      </c>
-      <c r="G54" s="1">
-        <v>46295</v>
-      </c>
-      <c r="H54" t="str">
+        <v>3100000071271</v>
+      </c>
+      <c r="G54" t="str">
+        <v>นายทดสอบ9 สมมติ</v>
+      </c>
+      <c r="H54" s="1">
+        <v>46290</v>
+      </c>
+      <c r="I54" s="1">
+        <v>46290</v>
+      </c>
+      <c r="J54" t="str">
         <v>UCS</v>
       </c>
-      <c r="I54">
-        <v>783</v>
-      </c>
-      <c r="J54">
-        <v>783</v>
-      </c>
       <c r="K54" t="str">
         <v/>
       </c>
       <c r="L54">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="M54">
         <v>0</v>
@@ -3504,7 +4178,7 @@
         <v>0</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>288</v>
       </c>
       <c r="P54">
         <v>0</v>
@@ -3516,48 +4190,78 @@
         <v>0</v>
       </c>
       <c r="S54">
-        <v>0</v>
+        <v>3360</v>
       </c>
       <c r="T54">
         <v>0</v>
+      </c>
+      <c r="U54">
+        <v>0</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0</v>
+      </c>
+      <c r="X54">
+        <v>0</v>
+      </c>
+      <c r="Y54">
+        <v>0</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+      <c r="AA54">
+        <v>0</v>
+      </c>
+      <c r="AB54">
+        <v>0</v>
+      </c>
+      <c r="AC54">
+        <v>0</v>
+      </c>
+      <c r="AD54">
+        <v>3648</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B55" t="str">
-        <v>T260930000089</v>
+        <v>6909001</v>
+      </c>
+      <c r="B55">
+        <v>41</v>
       </c>
       <c r="C55" t="str">
-        <v>000000024</v>
+        <v>T260925000054</v>
       </c>
       <c r="D55" t="str">
-        <v/>
+        <v>000000019</v>
       </c>
       <c r="E55" t="str">
-        <v>3100000190056</v>
+        <v/>
       </c>
       <c r="F55" t="str">
-        <v>นางทดสอบ24 สมมติ</v>
+        <v>3100000150461</v>
       </c>
       <c r="G55" t="str">
-        <v>30/09/2569</v>
+        <v>นายทดสอบ19 สมมติ</v>
       </c>
       <c r="H55" t="str">
+        <v>25/09/2569</v>
+      </c>
+      <c r="I55" t="str">
+        <v>25/09/2569</v>
+      </c>
+      <c r="J55" t="str">
         <v>UCS</v>
       </c>
-      <c r="I55">
-        <v>413</v>
-      </c>
-      <c r="J55">
-        <v>413</v>
-      </c>
       <c r="K55" t="str">
         <v/>
       </c>
       <c r="L55">
-        <v>0</v>
+        <v>718</v>
       </c>
       <c r="M55">
         <v>0</v>
@@ -3566,7 +4270,7 @@
         <v>0</v>
       </c>
       <c r="O55">
-        <v>0</v>
+        <v>598</v>
       </c>
       <c r="P55">
         <v>0</v>
@@ -3582,133 +4286,988 @@
       </c>
       <c r="T55">
         <v>0</v>
+      </c>
+      <c r="U55">
+        <v>0</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0</v>
+      </c>
+      <c r="X55">
+        <v>0</v>
+      </c>
+      <c r="Y55">
+        <v>0</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+      <c r="AA55">
+        <v>0</v>
+      </c>
+      <c r="AB55">
+        <v>0</v>
+      </c>
+      <c r="AC55">
+        <v>0</v>
+      </c>
+      <c r="AD55">
+        <v>598</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>6909001</v>
-      </c>
-      <c r="B56" t="str">
-        <v>T999999000001</v>
+        <v>6909002</v>
+      </c>
+      <c r="B56">
+        <v>42</v>
       </c>
       <c r="C56" t="str">
-        <v>000099999</v>
+        <v>T260925000084</v>
       </c>
       <c r="D56" t="str">
-        <v/>
+        <v>000000029</v>
       </c>
       <c r="E56" t="str">
-        <v>3999999999991</v>
+        <v/>
       </c>
       <c r="F56" t="str">
-        <v>นายนอก ระบบ</v>
+        <v>3100000229651</v>
       </c>
       <c r="G56" t="str">
-        <v>10/09/2569</v>
-      </c>
-      <c r="H56" t="str">
+        <v>นายทดสอบ29 สมมติ</v>
+      </c>
+      <c r="H56" s="1">
+        <v>46290</v>
+      </c>
+      <c r="I56" s="1">
+        <v>46290</v>
+      </c>
+      <c r="J56" t="str">
         <v>UCS</v>
       </c>
-      <c r="I56">
-        <v>500</v>
-      </c>
-      <c r="J56">
-        <v>500</v>
-      </c>
       <c r="K56" t="str">
         <v/>
+      </c>
+      <c r="L56">
+        <v>908</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>0</v>
+      </c>
+      <c r="O56">
+        <v>908</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+      <c r="Q56">
+        <v>0</v>
+      </c>
+      <c r="R56">
+        <v>2800</v>
+      </c>
+      <c r="S56">
+        <v>0</v>
+      </c>
+      <c r="T56">
+        <v>0</v>
+      </c>
+      <c r="U56">
+        <v>0</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0</v>
+      </c>
+      <c r="X56">
+        <v>0</v>
+      </c>
+      <c r="Y56">
+        <v>0</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+      <c r="AA56">
+        <v>0</v>
+      </c>
+      <c r="AB56">
+        <v>0</v>
+      </c>
+      <c r="AC56">
+        <v>0</v>
+      </c>
+      <c r="AD56">
+        <v>3708</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>6909002</v>
-      </c>
-      <c r="B57" t="str">
-        <v>T999999000002</v>
+        <v>6909003</v>
+      </c>
+      <c r="B57">
+        <v>43</v>
       </c>
       <c r="C57" t="str">
-        <v>000099998</v>
+        <v>T260928000027</v>
       </c>
       <c r="D57" t="str">
-        <v/>
+        <v>000000030</v>
       </c>
       <c r="E57" t="str">
-        <v>3999999999992</v>
+        <v/>
       </c>
       <c r="F57" t="str">
-        <v>นางนอก ระบบ</v>
+        <v>3100000237570</v>
       </c>
       <c r="G57" t="str">
-        <v>20/09/2569</v>
+        <v>นางทดสอบ30 สมมติ</v>
       </c>
       <c r="H57" t="str">
+        <v>28/09/2569</v>
+      </c>
+      <c r="I57" t="str">
+        <v>28/09/2569</v>
+      </c>
+      <c r="J57" t="str">
         <v>UCS</v>
       </c>
-      <c r="I57">
-        <v>650</v>
-      </c>
-      <c r="J57">
-        <v>0</v>
-      </c>
       <c r="K57" t="str">
-        <v>C301</v>
+        <v/>
+      </c>
+      <c r="L57">
+        <v>399</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>0</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+      <c r="Q57">
+        <v>0</v>
+      </c>
+      <c r="R57">
+        <v>0</v>
+      </c>
+      <c r="S57">
+        <v>0</v>
+      </c>
+      <c r="T57">
+        <v>240</v>
+      </c>
+      <c r="U57">
+        <v>0</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0</v>
+      </c>
+      <c r="X57">
+        <v>0</v>
+      </c>
+      <c r="Y57">
+        <v>0</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+      <c r="AA57">
+        <v>0</v>
+      </c>
+      <c r="AB57">
+        <v>0</v>
+      </c>
+      <c r="AC57">
+        <v>0</v>
+      </c>
+      <c r="AD57">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>6909001</v>
+      </c>
+      <c r="B58">
+        <v>44</v>
+      </c>
+      <c r="C58" t="str">
+        <v>T260928000057</v>
+      </c>
+      <c r="D58" t="str">
+        <v>000000040</v>
+      </c>
+      <c r="E58" t="str">
+        <v/>
+      </c>
+      <c r="F58" t="str">
+        <v>3100000316760</v>
+      </c>
+      <c r="G58" t="str">
+        <v>นางทดสอบ40 สมมติ</v>
+      </c>
+      <c r="H58" s="1">
+        <v>46293</v>
+      </c>
+      <c r="I58" s="1">
+        <v>46293</v>
+      </c>
+      <c r="J58" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K58" t="str">
+        <v/>
+      </c>
+      <c r="L58">
+        <v>709</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>0</v>
+      </c>
+      <c r="O58">
+        <v>709</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+      <c r="Q58">
+        <v>0</v>
+      </c>
+      <c r="R58">
+        <v>0</v>
+      </c>
+      <c r="S58">
+        <v>0</v>
+      </c>
+      <c r="T58">
+        <v>0</v>
+      </c>
+      <c r="U58">
+        <v>0</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0</v>
+      </c>
+      <c r="X58">
+        <v>0</v>
+      </c>
+      <c r="Y58">
+        <v>0</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+      <c r="AA58">
+        <v>0</v>
+      </c>
+      <c r="AB58">
+        <v>0</v>
+      </c>
+      <c r="AC58">
+        <v>0</v>
+      </c>
+      <c r="AD58">
+        <v>709</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v/>
-      </c>
-      <c r="B59" t="str">
-        <v/>
+        <v>6909002</v>
+      </c>
+      <c r="B59">
+        <v>45</v>
       </c>
       <c r="C59" t="str">
-        <v/>
+        <v>T260928000087</v>
       </c>
       <c r="D59" t="str">
-        <v/>
+        <v>000000010</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v/>
+        <v>3100000079190</v>
       </c>
       <c r="G59" t="str">
-        <v/>
+        <v>นางทดสอบ10 สมมติ</v>
       </c>
       <c r="H59" t="str">
-        <v>รวม</v>
+        <v>28/09/2569</v>
       </c>
       <c r="I59" t="str">
-        <v/>
+        <v>28/09/2569</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>UCS</v>
       </c>
       <c r="K59" t="str">
         <v/>
       </c>
+      <c r="L59">
+        <v>219</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>219</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+      <c r="Q59">
+        <v>0</v>
+      </c>
+      <c r="R59">
+        <v>0</v>
+      </c>
+      <c r="S59">
+        <v>0</v>
+      </c>
+      <c r="T59">
+        <v>0</v>
+      </c>
+      <c r="U59">
+        <v>0</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0</v>
+      </c>
+      <c r="X59">
+        <v>0</v>
+      </c>
+      <c r="Y59">
+        <v>0</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+      <c r="AA59">
+        <v>0</v>
+      </c>
+      <c r="AB59">
+        <v>0</v>
+      </c>
+      <c r="AC59">
+        <v>0</v>
+      </c>
+      <c r="AD59">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>6909003</v>
+      </c>
+      <c r="B60">
+        <v>46</v>
+      </c>
+      <c r="C60" t="str">
+        <v>T260929000028</v>
+      </c>
+      <c r="D60" t="str">
+        <v>000000037</v>
+      </c>
+      <c r="E60" t="str">
+        <v/>
+      </c>
+      <c r="F60" t="str">
+        <v>3100000293003</v>
+      </c>
+      <c r="G60" t="str">
+        <v>นายทดสอบ37 สมมติ</v>
+      </c>
+      <c r="H60" s="1">
+        <v>46294</v>
+      </c>
+      <c r="I60" s="1">
+        <v>46294</v>
+      </c>
+      <c r="J60" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K60" t="str">
+        <v/>
+      </c>
+      <c r="L60">
+        <v>436</v>
+      </c>
+      <c r="M60">
+        <v>0</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>436</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+      <c r="Q60">
+        <v>0</v>
+      </c>
+      <c r="R60">
+        <v>2800</v>
+      </c>
+      <c r="S60">
+        <v>0</v>
+      </c>
+      <c r="T60">
+        <v>0</v>
+      </c>
+      <c r="U60">
+        <v>0</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0</v>
+      </c>
+      <c r="X60">
+        <v>0</v>
+      </c>
+      <c r="Y60">
+        <v>0</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+      <c r="AA60">
+        <v>0</v>
+      </c>
+      <c r="AB60">
+        <v>0</v>
+      </c>
+      <c r="AC60">
+        <v>0</v>
+      </c>
+      <c r="AD60">
+        <v>3236</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>6909001</v>
+      </c>
+      <c r="B61">
+        <v>47</v>
+      </c>
+      <c r="C61" t="str">
+        <v>T260929000058</v>
+      </c>
+      <c r="D61" t="str">
+        <v>000000007</v>
+      </c>
+      <c r="E61" t="str">
+        <v/>
+      </c>
+      <c r="F61" t="str">
+        <v>3100000055433</v>
+      </c>
+      <c r="G61" t="str">
+        <v>นายทดสอบ7 สมมติ</v>
+      </c>
+      <c r="H61" t="str">
+        <v>29/09/2569</v>
+      </c>
+      <c r="I61" t="str">
+        <v>29/09/2569</v>
+      </c>
+      <c r="J61" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K61" t="str">
+        <v/>
+      </c>
+      <c r="L61">
+        <v>746</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>0</v>
+      </c>
+      <c r="O61">
+        <v>746</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+      <c r="Q61">
+        <v>0</v>
+      </c>
+      <c r="R61">
+        <v>0</v>
+      </c>
+      <c r="S61">
+        <v>0</v>
+      </c>
+      <c r="T61">
+        <v>0</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0</v>
+      </c>
+      <c r="X61">
+        <v>0</v>
+      </c>
+      <c r="Y61">
+        <v>0</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+      <c r="AA61">
+        <v>0</v>
+      </c>
+      <c r="AB61">
+        <v>0</v>
+      </c>
+      <c r="AC61">
+        <v>0</v>
+      </c>
+      <c r="AD61">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="str">
+        <v>6909002</v>
+      </c>
+      <c r="B62">
+        <v>48</v>
+      </c>
+      <c r="C62" t="str">
+        <v>T260929000088</v>
+      </c>
+      <c r="D62" t="str">
+        <v>000000017</v>
+      </c>
+      <c r="E62" t="str">
+        <v/>
+      </c>
+      <c r="F62" t="str">
+        <v>3100000134623</v>
+      </c>
+      <c r="G62" t="str">
+        <v>นายทดสอบ17 สมมติ</v>
+      </c>
+      <c r="H62" s="1">
+        <v>46294</v>
+      </c>
+      <c r="I62" s="1">
+        <v>46294</v>
+      </c>
+      <c r="J62" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K62" t="str">
+        <v/>
+      </c>
+      <c r="L62">
+        <v>256</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>256</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+      <c r="Q62">
+        <v>0</v>
+      </c>
+      <c r="R62">
+        <v>0</v>
+      </c>
+      <c r="S62">
+        <v>3360</v>
+      </c>
+      <c r="T62">
+        <v>0</v>
+      </c>
+      <c r="U62">
+        <v>0</v>
+      </c>
+      <c r="V62">
+        <v>2240</v>
+      </c>
+      <c r="W62">
+        <v>0</v>
+      </c>
+      <c r="X62">
+        <v>0</v>
+      </c>
+      <c r="Y62">
+        <v>0</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+      <c r="AA62">
+        <v>0</v>
+      </c>
+      <c r="AB62">
+        <v>0</v>
+      </c>
+      <c r="AC62">
+        <v>0</v>
+      </c>
+      <c r="AD62">
+        <v>5856</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="str">
+        <v>6909001</v>
+      </c>
+      <c r="B63">
+        <v>49</v>
+      </c>
+      <c r="C63" t="str">
+        <v>T260930000059</v>
+      </c>
+      <c r="D63" t="str">
+        <v>000000014</v>
+      </c>
+      <c r="E63" t="str">
+        <v/>
+      </c>
+      <c r="F63" t="str">
+        <v>3100000110866</v>
+      </c>
+      <c r="G63" t="str">
+        <v>นางทดสอบ14 สมมติ</v>
+      </c>
+      <c r="H63" s="1">
+        <v>46295</v>
+      </c>
+      <c r="I63" s="1">
+        <v>46295</v>
+      </c>
+      <c r="J63" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K63" t="str">
+        <v/>
+      </c>
+      <c r="L63">
+        <v>783</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>0</v>
+      </c>
+      <c r="O63">
+        <v>783</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+      <c r="Q63">
+        <v>0</v>
+      </c>
+      <c r="R63">
+        <v>0</v>
+      </c>
+      <c r="S63">
+        <v>0</v>
+      </c>
+      <c r="T63">
+        <v>0</v>
+      </c>
+      <c r="U63">
+        <v>0</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0</v>
+      </c>
+      <c r="X63">
+        <v>0</v>
+      </c>
+      <c r="Y63">
+        <v>0</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+      <c r="AA63">
+        <v>0</v>
+      </c>
+      <c r="AB63">
+        <v>0</v>
+      </c>
+      <c r="AC63">
+        <v>0</v>
+      </c>
+      <c r="AD63">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>6909002</v>
+      </c>
+      <c r="B64">
+        <v>50</v>
+      </c>
+      <c r="C64" t="str">
+        <v>T260930000089</v>
+      </c>
+      <c r="D64" t="str">
+        <v>000000024</v>
+      </c>
+      <c r="E64" t="str">
+        <v/>
+      </c>
+      <c r="F64" t="str">
+        <v>3100000190056</v>
+      </c>
+      <c r="G64" t="str">
+        <v>นางทดสอบ24 สมมติ</v>
+      </c>
+      <c r="H64" t="str">
+        <v>30/09/2569</v>
+      </c>
+      <c r="I64" t="str">
+        <v>30/09/2569</v>
+      </c>
+      <c r="J64" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K64" t="str">
+        <v/>
+      </c>
+      <c r="L64">
+        <v>413</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>293</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+      <c r="Q64">
+        <v>0</v>
+      </c>
+      <c r="R64">
+        <v>0</v>
+      </c>
+      <c r="S64">
+        <v>0</v>
+      </c>
+      <c r="T64">
+        <v>0</v>
+      </c>
+      <c r="U64">
+        <v>0</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0</v>
+      </c>
+      <c r="X64">
+        <v>0</v>
+      </c>
+      <c r="Y64">
+        <v>0</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+      <c r="AA64">
+        <v>0</v>
+      </c>
+      <c r="AB64">
+        <v>0</v>
+      </c>
+      <c r="AC64">
+        <v>0</v>
+      </c>
+      <c r="AD64">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="str">
+        <v>6909001</v>
+      </c>
+      <c r="B65">
+        <v>51</v>
+      </c>
+      <c r="C65" t="str">
+        <v>T999999000001</v>
+      </c>
+      <c r="D65" t="str">
+        <v>000099999</v>
+      </c>
+      <c r="E65" t="str">
+        <v/>
+      </c>
+      <c r="F65" t="str">
+        <v>3999999999991</v>
+      </c>
+      <c r="G65" t="str">
+        <v>นายนอก ระบบ</v>
+      </c>
+      <c r="H65" t="str">
+        <v>10/09/2569</v>
+      </c>
+      <c r="I65" t="str">
+        <v>10/09/2569</v>
+      </c>
+      <c r="J65" t="str">
+        <v>UCS</v>
+      </c>
+      <c r="K65" t="str">
+        <v/>
+      </c>
+      <c r="L65">
+        <v>500</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+      <c r="Q65">
+        <v>0</v>
+      </c>
+      <c r="R65">
+        <v>400</v>
+      </c>
+      <c r="S65">
+        <v>0</v>
+      </c>
+      <c r="T65">
+        <v>0</v>
+      </c>
+      <c r="U65">
+        <v>0</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0</v>
+      </c>
+      <c r="X65">
+        <v>0</v>
+      </c>
+      <c r="Y65">
+        <v>0</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+      <c r="AA65">
+        <v>0</v>
+      </c>
+      <c r="AB65">
+        <v>0</v>
+      </c>
+      <c r="AC65">
+        <v>0</v>
+      </c>
+      <c r="AD65">
+        <v>400</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="L4:M4"/>
-    <mergeCell ref="N4:O4"/>
-    <mergeCell ref="P4:P5"/>
-    <mergeCell ref="Q4:T4"/>
+  <mergeCells count="25">
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="F12:F14"/>
+    <mergeCell ref="G12:G14"/>
+    <mergeCell ref="H12:H14"/>
+    <mergeCell ref="I12:I14"/>
+    <mergeCell ref="J12:J14"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="L12:L14"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="O12:AC12"/>
+    <mergeCell ref="O13:O14"/>
+    <mergeCell ref="P13:Q13"/>
+    <mergeCell ref="R13:S13"/>
+    <mergeCell ref="T13:U13"/>
+    <mergeCell ref="V13:V14"/>
+    <mergeCell ref="W13:Y13"/>
+    <mergeCell ref="Z13:Z14"/>
+    <mergeCell ref="AA13:AA14"/>
+    <mergeCell ref="AB13:AB14"/>
+    <mergeCell ref="AC13:AC14"/>
+    <mergeCell ref="AD12:AD14"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T59"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD65"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/samples/sample_rep_opd_2569-09.xlsx
+++ b/samples/sample_rep_opd_2569-09.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AD65"/>
+  <dimension ref="A1:AD82"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -5236,6 +5236,165 @@
       </c>
       <c r="AD65">
         <v>400</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="G66" t="str">
+        <v>รวม</v>
+      </c>
+      <c r="AD66">
+        <v>72098</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="str">
+        <v>สรุปการจ่ายชดเชย</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="str">
+        <v>OP</v>
+      </c>
+      <c r="B73" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C73">
+        <v>10</v>
+      </c>
+      <c r="F73">
+        <v>1000</v>
+      </c>
+      <c r="H73" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="str">
+        <v>IP</v>
+      </c>
+      <c r="B74" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C74">
+        <v>11</v>
+      </c>
+      <c r="F74">
+        <v>2000</v>
+      </c>
+      <c r="H74" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="str">
+        <v>HC</v>
+      </c>
+      <c r="B75" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C75">
+        <v>12</v>
+      </c>
+      <c r="F75">
+        <v>3000</v>
+      </c>
+      <c r="H75" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="str">
+        <v>AE</v>
+      </c>
+      <c r="B76" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C76">
+        <v>13</v>
+      </c>
+      <c r="F76">
+        <v>4000</v>
+      </c>
+      <c r="H76" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="str">
+        <v>INST</v>
+      </c>
+      <c r="B77" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C77">
+        <v>14</v>
+      </c>
+      <c r="F77">
+        <v>5000</v>
+      </c>
+      <c r="H77" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="str">
+        <v>DMIS</v>
+      </c>
+      <c r="B78" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C78">
+        <v>15</v>
+      </c>
+      <c r="F78">
+        <v>6000</v>
+      </c>
+      <c r="H78" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="str">
+        <v>PP</v>
+      </c>
+      <c r="B79" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C79">
+        <v>16</v>
+      </c>
+      <c r="F79">
+        <v>7000</v>
+      </c>
+      <c r="H79" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="str">
+        <v>FS</v>
+      </c>
+      <c r="B80" t="str">
+        <v>จำนวนราย</v>
+      </c>
+      <c r="C80">
+        <v>17</v>
+      </c>
+      <c r="F80">
+        <v>8000</v>
+      </c>
+      <c r="H80" t="str">
+        <v>01/08/2569</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="str">
+        <v>หมายเหตุ: ข้อมูลตัวอย่าง</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="str">
+        <v>ผู้จัดทำรายงาน ...........</v>
       </c>
     </row>
   </sheetData>
@@ -5267,7 +5426,7 @@
     <mergeCell ref="AD12:AD14"/>
   </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AD65"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AD82"/>
   </ignoredErrors>
 </worksheet>
 </file>